--- a/ChiangMai_ChiangRai_12_Districts_Landmarks.xlsx
+++ b/ChiangMai_ChiangRai_12_Districts_Landmarks.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G248"/>
+  <dimension ref="A1:G249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2543,27 +2543,27 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Ploen Ruedee Night Market</t>
+          <t>阿努善老牌泰國燕窩 1號店 (รังนกไทย สาขา 1 / Thai Bird's Nest)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>美食廣場夜市</t>
+          <t>特色名店甜品</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>草地露天啤酒花園、多國美食餐車與現場樂團表演</t>
+          <t>阿努善夜市老字號！現燉金絲燕窩、椰奶燕窩、雪蛤與白果甜品，逛夜市必嚐暖心滋補甜品</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Night Bazaar 核心</t>
+          <t>長康路/阿努善夜市內</t>
         </is>
       </c>
     </row>
@@ -2578,27 +2578,27 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Woo Cafe &amp; Art Gallery</t>
+          <t>Ploen Ruedee Night Market</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>網美景觀咖啡</t>
+          <t>美食廣場夜市</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>湄平河畔畫廊風綠意咖啡館、精緻泰式下午茶與生活選物</t>
+          <t>草地露天啤酒花園、多國美食餐車與現場樂團表演</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>氣氛極佳質感咖啡館</t>
+          <t>Night Bazaar 核心</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>The Baristro x Ping River</t>
+          <t>Woo Cafe &amp; Art Gallery</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>網美水岸咖啡</t>
+          <t>網美景觀咖啡</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>湄平河畔極簡幾何木質玻璃屋、水岸露天咖啡座與特調甜點</t>
+          <t>湄平河畔畫廊風綠意咖啡館、精緻泰式下午茶與生活選物</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>河畔景觀第一排</t>
+          <t>氣氛極佳質感咖啡館</t>
         </is>
       </c>
     </row>
@@ -2648,17 +2648,17 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>My Grandparent's House (老奶奶木屋)</t>
+          <t>The Baristro x Ping River</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>古木屋河畔咖啡</t>
+          <t>網美水岸咖啡</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>百年泰式傳統雙層木屋、臨河涼亭與古早味泰式甜點</t>
+          <t>湄平河畔極簡幾何木質玻璃屋、水岸露天咖啡座與特調甜點</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>平河西岸老街</t>
+          <t>河畔景觀第一排</t>
         </is>
       </c>
     </row>
@@ -2683,27 +2683,27 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>The Riverside Bar &amp; Restaurant</t>
+          <t>My Grandparent's House (老奶奶木屋)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>美饌景觀餐廳</t>
+          <t>古木屋河畔咖啡</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>湄平河畔現場爵士樂演奏、水岸景觀晚餐與精釀啤酒</t>
+          <t>百年泰式傳統雙層木屋、臨河涼亭與古早味泰式甜點</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>夜晚氣氛絕佳</t>
+          <t>平河西岸老街</t>
         </is>
       </c>
     </row>
@@ -2718,17 +2718,17 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Good View Chiang Mai</t>
+          <t>The Riverside Bar &amp; Restaurant</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>河畔景觀餐廳</t>
+          <t>美饌景觀餐廳</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>清邁三十年老牌河畔美饌、現場樂團演唱與泰式海鮮料理</t>
+          <t>湄平河畔現場爵士樂演奏、水岸景觀晚餐與精釀啤酒</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>晚餐熱門</t>
+          <t>夜晚氣氛絕佳</t>
         </is>
       </c>
     </row>
@@ -2753,17 +2753,17 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Nakara Jardin</t>
+          <t>Good View Chiang Mai</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>河畔法式下午茶</t>
+          <t>河畔景觀餐廳</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>平河畔隱密法式花園、精緻司康、法式甜點與英式下午茶</t>
+          <t>清邁三十年老牌河畔美饌、現場樂團演唱與泰式海鮮料理</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>河畔極奢華體驗</t>
+          <t>晚餐熱門</t>
         </is>
       </c>
     </row>
@@ -2788,27 +2788,27 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Khun Kae's Juice Bar</t>
+          <t>Nakara Jardin</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>健康果昔名店</t>
+          <t>河畔法式下午茶</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>瓦洛洛周邊超高人氣純天然現打果昔碗與熱帶水果杯</t>
+          <t>平河畔隱密法式花園、精緻司康、法式甜點與英式下午茶</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>0.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>健康甜點首選</t>
+          <t>河畔極奢華體驗</t>
         </is>
       </c>
     </row>
@@ -2823,27 +2823,27 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>泰香閣餐廳 (The Service 1921 Anantara)</t>
+          <t>Khun Kae's Juice Bar</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>奢華水岸美饌</t>
+          <t>健康果昔名店</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>阿南塔拉度假村內英倫特務風格奢華河畔泰菜與下午茶</t>
+          <t>瓦洛洛周邊超高人氣純天然現打果昔碗與熱帶水果杯</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>0.5 小時</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>湄平河東岸</t>
+          <t>健康甜點首選</t>
         </is>
       </c>
     </row>
@@ -2858,17 +2858,17 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Let's Relax Spa (長康路 Night Bazaar 店)</t>
+          <t>泰香閣餐廳 (The Service 1921 Anantara)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>知名連鎖水療</t>
+          <t>奢華水岸美饌</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>泰國知名連鎖水療品牌、草藥球按摩與芒果糯米飯招待</t>
+          <t>阿南塔拉度假村內英倫特務風格奢華河畔泰菜與下午茶</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>夜市旁最便利</t>
+          <t>湄平河東岸</t>
         </is>
       </c>
     </row>
@@ -2893,27 +2893,27 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>卡拉爾夜市美食廣場 (Kalare Night Bazaar)</t>
+          <t>Let's Relax Spa (長康路 Night Bazaar 店)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>夜市美食</t>
+          <t>知名連鎖水療</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>長康路夜市室內美食廣場、泰式小吃與露天傳統舞蹈</t>
+          <t>泰國知名連鎖水療品牌、草藥球按摩與芒果糯米飯招待</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>夜市核心</t>
+          <t>夜市旁最便利</t>
         </is>
       </c>
     </row>
@@ -2928,17 +2928,17 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Looper Co. (復古洗車廠酒吧咖啡)</t>
+          <t>卡拉爾夜市美食廣場 (Kalare Night Bazaar)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>爆款網美咖啡</t>
+          <t>夜市美食</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>白天是極簡冷萃咖啡館、晚上變身為水泥復古美式調酒吧</t>
+          <t>長康路夜市室內美食廣場、泰式小吃與露天傳統舞蹈</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -2948,42 +2948,42 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>昌莫區</t>
+          <t>夜市核心</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>3_清邁古城南區與機場商圈</t>
+          <t>2_清邁湄平河與瓦洛洛區</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Kasetsorn Vegetarian (เกษตรสรณ์ 平價素食)</t>
+          <t>Looper Co. (復古洗車廠酒吧咖啡)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>素食/純素餐廳</t>
+          <t>爆款網美咖啡</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>清邁在地人最愛平價泰式素食自助餐！數十道純素泰式打拋素肉、素咖哩與炸物</t>
+          <t>白天是極簡冷萃咖啡館、晚上變身為水泥復古美式調酒吧</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>南門外平價首選</t>
+          <t>昌莫區</t>
         </is>
       </c>
     </row>
@@ -2998,27 +2998,27 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>素攀純銀廟 (Wat Sri Suphan)</t>
+          <t>Kasetsorn Vegetarian (เกษตรสรณ์ 平價素食)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>古蹟/寺廟</t>
+          <t>素食/純素餐廳</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>全世界唯一純銀浮雕主殿！夜間點燈與金屬手工藝村</t>
+          <t>清邁在地人最愛平價泰式素食自助餐！數十道純素泰式打拋素肉、素咖哩與炸物</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>銀廟主殿限男性進入，女眷可在外拍照</t>
+          <t>南門外平價首選</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>週六瓦萊路銀器夜市 (Wua Lai Night Market)</t>
+          <t>素攀純銀廟 (Wat Sri Suphan)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>傳統夜市/購物</t>
+          <t>古蹟/寺廟</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>沿著銀器街展開、傳統金屬工藝與飾品採買</t>
+          <t>全世界唯一純銀浮雕主殿！夜間點燈與金屬手工藝村</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>週六 17:00 開攤</t>
+          <t>銀廟主殿限男性進入，女眷可在外拍照</t>
         </is>
       </c>
     </row>
@@ -3068,27 +3068,27 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>松達寺 (Wat Suan Dok / 白塔寺)</t>
+          <t>週六瓦萊路銀器夜市 (Wua Lai Night Market)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>古蹟/寺廟</t>
+          <t>傳統夜市/購物</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>絕美純白皇室塔林與夕陽金光、蘭納歷代國王陵墓</t>
+          <t>沿著銀器街展開、傳統金屬工藝與飾品採買</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>古城西南門外</t>
+          <t>週六 17:00 開攤</t>
         </is>
       </c>
     </row>
@@ -3103,27 +3103,27 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>清邁國際機場 (CNX)</t>
+          <t>松達寺 (Wat Suan Dok / 白塔寺)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>交通航站</t>
+          <t>古蹟/寺廟</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>泰北第一大空中樞紐、國際與國內線接送機</t>
+          <t>絕美純白皇室塔林與夕陽金光、蘭納歷代國王陵墓</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>離古城 10 分鐘</t>
+          <t>古城西南門外</t>
         </is>
       </c>
     </row>
@@ -3138,27 +3138,27 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Central Chiang Mai Airport 商場</t>
+          <t>清邁國際機場 (CNX)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>購物百貨</t>
+          <t>交通航站</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>機場旁大型綜合商場、離境前伴手禮與泰國手標奶茶採買</t>
+          <t>泰北第一大空中樞紐、國際與國內線接送機</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>地下一樓美食街極讚</t>
+          <t>離古城 10 分鐘</t>
         </is>
       </c>
     </row>
@@ -3173,17 +3173,17 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>Premium Outlet Chiang Mai</t>
+          <t>Central Chiang Mai Airport 商場</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>折扣購物中心</t>
+          <t>購物百貨</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>美式 Outlet 購物村、各大運動品牌與服飾超值折扣</t>
+          <t>機場旁大型綜合商場、離境前伴手禮與泰國手標奶茶採買</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>機場往南公路旁</t>
+          <t>地下一樓美食街極讚</t>
         </is>
       </c>
     </row>
@@ -3208,27 +3208,27 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Nim City Daily (有機市集商場)</t>
+          <t>Premium Outlet Chiang Mai</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>生活美食廣場</t>
+          <t>折扣購物中心</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>有機農夫超市 Rimping、小龍包與各式文青輕食餐廳</t>
+          <t>美式 Outlet 購物村、各大運動品牌與服飾超值折扣</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>機場旁生活圈</t>
+          <t>機場往南公路旁</t>
         </is>
       </c>
     </row>
@@ -3243,17 +3243,17 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>瓦萊手工銀器村 (Wua Lai Silversmith Village)</t>
+          <t>Nim City Daily (有機市集商場)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>工藝體驗</t>
+          <t>生活美食廣場</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>百年銀器雕刻工坊、師傅現場打磨銀盤與銀首飾</t>
+          <t>有機農夫超市 Rimping、小龍包與各式文青輕食餐廳</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>瓦萊路巷弄</t>
+          <t>機場旁生活圈</t>
         </is>
       </c>
     </row>
@@ -3278,27 +3278,27 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Kad Manee Market (湖畔夜市)</t>
+          <t>瓦萊手工銀器村 (Wua Lai Silversmith Village)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>傳統夜市/美食</t>
+          <t>工藝體驗</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>機場旁湖畔景觀夜市、竹編涼亭與在地泰式小吃</t>
+          <t>百年銀器雕刻工坊、師傅現場打磨銀盤與銀首飾</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>在地人最愛夜市</t>
+          <t>瓦萊路巷弄</t>
         </is>
       </c>
     </row>
@@ -3313,27 +3313,27 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>清邁南門小吃街 (Chiang Mai Gate Night Market)</t>
+          <t>Kad Manee Market (湖畔夜市)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>夜市小吃</t>
+          <t>傳統夜市/美食</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>古城南門外夜間小吃攤、炸雞、芒果糯米飯與泰式炒河粉</t>
+          <t>機場旁湖畔景觀夜市、竹編涼亭與在地泰式小吃</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>天天營業</t>
+          <t>在地人最愛夜市</t>
         </is>
       </c>
     </row>
@@ -3348,17 +3348,17 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>清邁南門傳統早市 (Chiang Mai Gate Morning Market)</t>
+          <t>清邁南門小吃街 (Chiang Mai Gate Night Market)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>傳統早市</t>
+          <t>夜市小吃</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>古城南門清晨傳統早市、僧侶托缽祈福與道地泰式早餐</t>
+          <t>古城南門外夜間小吃攤、炸雞、芒果糯米飯與泰式炒河粉</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>早晨 06:00 ~ 09:00</t>
+          <t>天天營業</t>
         </is>
       </c>
     </row>
@@ -3383,62 +3383,62 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Oasis Spa (綠野仙蹤蘭納館)</t>
+          <t>清邁南門傳統早市 (Chiang Mai Gate Morning Market)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>奢華頂級水療</t>
+          <t>傳統早市</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>阿勛精選推薦！蘭納奢華庭園、四手按摩與精油水療</t>
+          <t>古城南門清晨傳統早市、僧侶托缽祈福與道地泰式早餐</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>需提前預約</t>
+          <t>早晨 06:00 ~ 09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>4_尼曼潮流區與清大商圈</t>
+          <t>3_清邁古城南區與機場商圈</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>One Nimman (尼曼一號)</t>
+          <t>Oasis Spa (綠野仙蹤蘭納館)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>購物商場/文青商場</t>
+          <t>奢華頂級水療</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>歐式磚紅鐘樓廣場、文青手作市集、美食街與露天酒吧</t>
+          <t>阿勛精選推薦！蘭納奢華庭園、四手按摩與精油水療</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>拍照極美</t>
+          <t>需提前預約</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>MAYA 頂級購物中心 (MAYA Mall)</t>
+          <t>One Nimman (尼曼一號)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>購物商場/百貨地標</t>
+          <t>購物商場/文青商場</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>尼曼地標購物中心、24小時 C.A.M.P 空間、頂樓露天酒吧觀景</t>
+          <t>歐式磚紅鐘樓廣場、文青手作市集、美食街與露天酒吧</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>地下美食街極便宜</t>
+          <t>拍照極美</t>
         </is>
       </c>
     </row>
@@ -3488,27 +3488,27 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Nihon Seishin Vegan Ramen (日本精神純素拉麵)</t>
+          <t>MAYA 頂級購物中心 (MAYA Mall)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>素食/純素餐廳</t>
+          <t>購物商場/百貨地標</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>尼曼區極致日式純素拉麵！濃郁純素豆乳豚骨湯頭、純素叉燒與純素日式餃子</t>
+          <t>尼曼地標購物中心、24小時 C.A.M.P 空間、頂樓露天酒吧觀景</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>尼曼區知名純素拉麵</t>
+          <t>地下美食街極便宜</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>The Vegano Chiang Mai</t>
+          <t>Nihon Seishin Vegan Ramen (日本精神純素拉麵)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>尼曼巷弄極簡美式純素漢堡、植物肉熱狗堡與純素奶昔</t>
+          <t>尼曼區極致日式純素拉麵！濃郁純素豆乳豚骨湯頭、純素叉燒與純素日式餃子</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>尼曼區</t>
+          <t>尼曼區知名純素拉麵</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Bee Vegan (清大學生平價純素餐廳)</t>
+          <t>The Vegano Chiang Mai</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3568,17 +3568,17 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>清大後門學生極力推薦高 CP 值平價純素泰菜、純素綠咖哩與炸素雞</t>
+          <t>尼曼巷弄極簡美式純素漢堡、植物肉熱狗堡與純素奶昔</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>清大後門</t>
+          <t>尼曼區</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Anchan Vegetarian Restaurant</t>
+          <t>Bee Vegan (清大學生平價純素餐廳)</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3603,17 +3603,17 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>尼曼區極致有機蔬食餐廳！蝶豆花天然藍色飯、泰式純素炒河粉與香草溫沙拉</t>
+          <t>清大後門學生極力推薦高 CP 值平價純素泰菜、純素綠咖哩與炸素雞</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>尼曼區素食首選</t>
+          <t>清大後門</t>
         </is>
       </c>
     </row>
@@ -3628,17 +3628,17 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>MARS.cnx (火星沉浸式咖啡)</t>
+          <t>Anchan Vegetarian Restaurant</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>爆款網美咖啡</t>
+          <t>素食/純素餐廳</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>火星地質岩洞、宇宙太空艙與極光打卡背景、火星特調飲品</t>
+          <t>尼曼區極致有機蔬食餐廳！蝶豆花天然藍色飯、泰式純素炒河粉與香草溫沙拉</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>IG 熱門第一名</t>
+          <t>尼曼區素食首選</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>PLUTO Cafe (暗黑外太空咖啡)</t>
+          <t>MARS.cnx (火星沉浸式咖啡)</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>暗黑極簡水泥幾何建築、冥王星外太空風格與冷冽氛圍甜點</t>
+          <t>火星地質岩洞、宇宙太空艙與極光打卡背景、火星特調飲品</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>建築設計感極強</t>
+          <t>IG 熱門第一名</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Transit No.8 (日式跑道咖啡)</t>
+          <t>PLUTO Cafe (暗黑外太空咖啡)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>日式登機門與機場跑道設計、日式抹荼與特調冰淇淋咖啡</t>
+          <t>暗黑極簡水泥幾何建築、冥王星外太空風格與冷冽氛圍甜點</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>尼曼南側巷弄</t>
+          <t>建築設計感極強</t>
         </is>
       </c>
     </row>
@@ -3733,17 +3733,17 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Khao Soi Nimman (尼曼咖哩麵)</t>
+          <t>Transit No.8 (日式跑道咖啡)</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>米其林必比登美食</t>
+          <t>爆款網美咖啡</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>米其林必比登推薦！尼曼區最火爆豪華泰北咖哩麵、海鮮與牛腱雙拼</t>
+          <t>日式登機門與機場跑道設計、日式抹荼與特調冰淇淋咖啡</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>尼曼7巷</t>
+          <t>尼曼南側巷弄</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Guay Tiew Kua Gai Nimman (尼曼鐵板炒雞麵)</t>
+          <t>Khao Soi Nimman (尼曼咖哩麵)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3778,17 +3778,17 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>米其林必比登推薦！熱鐵板爆炒寬米粉與嫩雞肉、半熟蛋液焦香</t>
+          <t>米其林必比登推薦！尼曼區最火爆豪華泰北咖哩麵、海鮮與牛腱雙拼</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>尼曼6巷</t>
+          <t>尼曼7巷</t>
         </is>
       </c>
     </row>
@@ -3803,17 +3803,17 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Gopuek Kua-KAI (古樸炒雞麵)</t>
+          <t>Guay Tiew Kua Gai Nimman (尼曼鐵板炒雞麵)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>米其林推薦美食</t>
+          <t>米其林必比登美食</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>米其林推薦！尼曼後方經典古早味鑊氣鐵板炒雞麵與泰式奶茶</t>
+          <t>米其林必比登推薦！熱鐵板爆炒寬米粉與嫩雞肉、半熟蛋液焦香</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>早午餐名店</t>
+          <t>尼曼6巷</t>
         </is>
       </c>
     </row>
@@ -3838,17 +3838,17 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>清大附近燕窩 (泰榮/清大老字號燕窩)</t>
+          <t>Gopuek Kua-KAI (古樸炒雞麵)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>特色名店美食</t>
+          <t>米其林推薦美食</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>在地饕客激推！高 CP 值燉煮金絲燕窩與雪蛤甜品</t>
+          <t>米其林推薦！尼曼後方經典古早味鑊氣鐵板炒雞麵與泰式奶茶</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>清邁大學後門美食街</t>
+          <t>早午餐名店</t>
         </is>
       </c>
     </row>
@@ -3873,17 +3873,17 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Khao Soi Mae Sai (泰北咖哩麵)</t>
+          <t>清大附近燕窩 (泰榮/清大老字號燕窩)</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>米其林必比登美食</t>
+          <t>特色名店美食</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>米其林必比登推薦！濃郁椰奶咖哩濃湯、炸脆麵與嫩雞腿</t>
+          <t>在地饕客激推！高 CP 值燉煮金絲燕窩與雪蛤甜品</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>營業至 16:00 止</t>
+          <t>清邁大學後門美食街</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Huen Muan Jai (帝王餐拼盤)</t>
+          <t>Khao Soi Mae Sai (泰北咖哩麵)</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>連年米其林推薦！經典泰北帝王餐小吃拼盤、炸豬皮與泰北香腸</t>
+          <t>米其林必比登推薦！濃郁椰奶咖哩濃湯、炸脆麵與嫩雞腿</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>正宗泰北菜代表</t>
+          <t>營業至 16:00 止</t>
         </is>
       </c>
     </row>
@@ -3943,27 +3943,27 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Cherng Doi Roast Chicken</t>
+          <t>Huen Muan Jai (帝王餐拼盤)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>人氣燒烤美食</t>
+          <t>米其林必比登美食</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>獨門脆皮烤雞 (Kai Thong)、脆皮外表與多汁雞肉、糯米飯</t>
+          <t>連年米其林推薦！經典泰北帝王餐小吃拼盤、炸豬皮與泰北香腸</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>尼曼巷弄平價美食</t>
+          <t>正宗泰北菜代表</t>
         </is>
       </c>
     </row>
@@ -3978,27 +3978,27 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Tong Tem Toh (童添圖)</t>
+          <t>Cherng Doi Roast Chicken</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>人氣泰北燒烤</t>
+          <t>人氣燒烤美食</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>尼曼最火爆露天燒烤！泰北烤豬肉、酸肉煎蛋與泰北蔬菜湯</t>
+          <t>獨門脆皮烤雞 (Kai Thong)、脆皮外表與多汁雞肉、糯米飯</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>晚餐用餐時間大排長龍</t>
+          <t>尼曼巷弄平價美食</t>
         </is>
       </c>
     </row>
@@ -4013,27 +4013,27 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>蝶豆花藍色麵 (Anchan Noodle)</t>
+          <t>Tong Tem Toh (童添圖)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>特色網美美食</t>
+          <t>人氣泰北燒烤</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>蝶豆花天然染色的夢幻藍色泰式米粉湯與藍色椰香豬肉飯</t>
+          <t>尼曼最火爆露天燒烤！泰北烤豬肉、酸肉煎蛋與泰北蔬菜湯</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>尼曼巷弄內</t>
+          <t>晚餐用餐時間大排長龍</t>
         </is>
       </c>
     </row>
@@ -4048,17 +4048,17 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Ristr8to Lab / Graph Cafe</t>
+          <t>蝶豆花藍色麵 (Anchan Noodle)</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>網美精品咖啡</t>
+          <t>特色網美美食</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>世界拉花冠軍咖啡店、極簡工業風特調咖啡體驗</t>
+          <t>蝶豆花天然染色的夢幻藍色泰式米粉湯與藍色椰香豬肉飯</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>拉花圖案極精緻</t>
+          <t>尼曼巷弄內</t>
         </is>
       </c>
     </row>
@@ -4083,17 +4083,17 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Roast8ry Flagship Store</t>
+          <t>Ristr8to Lab / Graph Cafe</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>世界級冠軍咖啡</t>
+          <t>網美精品咖啡</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>世界咖啡大賽冠軍旗艦店、骷髏頭杯特調與自烘單品豆</t>
+          <t>世界拉花冠軍咖啡店、極簡工業風特調咖啡體驗</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>尼曼 17 巷</t>
+          <t>拉花圖案極精緻</t>
         </is>
       </c>
     </row>
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>GRAPH Ground</t>
+          <t>Roast8ry Flagship Store</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>工業暗黑風咖啡</t>
+          <t>世界級冠軍咖啡</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>挑高工業風玻璃烘豆室、沉浸式專業手沖與特調冷萃咖啡</t>
+          <t>世界咖啡大賽冠軍旗艦店、骷髏頭杯特調與自烘單品豆</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>尼曼周邊</t>
+          <t>尼曼 17 巷</t>
         </is>
       </c>
     </row>
@@ -4153,17 +4153,17 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>SS1254372 Cafe (圓窗太空艙咖啡)</t>
+          <t>GRAPH Ground</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>爆款藝文咖啡</t>
+          <t>工業暗黑風咖啡</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>巨大潛水艇圓窗設計、藝文畫廊空間與健康彩虹早午餐</t>
+          <t>挑高工業風玻璃烘豆室、沉浸式專業手沖與特調冷萃咖啡</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>尼曼巷弄名店</t>
+          <t>尼曼周邊</t>
         </is>
       </c>
     </row>
@@ -4188,17 +4188,17 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Yellow Crafts Cafe (日系豆乳咖啡)</t>
+          <t>SS1254372 Cafe (圓窗太空艙咖啡)</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>極簡文青咖啡</t>
+          <t>爆款藝文咖啡</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>亮黃色與純白日系幾何空間、自製新鮮濃郁豆乳咖啡與甜點</t>
+          <t>巨大潛水艇圓窗設計、藝文畫廊空間與健康彩虹早午餐</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>尼曼西南側</t>
+          <t>尼曼巷弄名店</t>
         </is>
       </c>
     </row>
@@ -4223,27 +4223,27 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Jing Jai Market (JJ Market / 綠色農夫市集)</t>
+          <t>Yellow Crafts Cafe (日系豆乳咖啡)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>文青手作市集</t>
+          <t>極簡文青咖啡</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>清邁每週末最紅的文青手作、手沖咖啡、農夫有機美食與手工藝</t>
+          <t>亮黃色與純白日系幾何空間、自製新鮮濃郁豆乳咖啡與甜點</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>週六日 06:00 ~ 13:00 限定</t>
+          <t>尼曼西南側</t>
         </is>
       </c>
     </row>
@@ -4258,27 +4258,27 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>瘋狂大碗麵 (Crazy Noodle)</t>
+          <t>Jing Jai Market (JJ Market / 綠色農夫市集)</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>特色平價小吃</t>
+          <t>文青手作市集</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>浮誇巨型海鮮與巨型豬肋排泰式酸辣麵碗、自選湯頭麵條</t>
+          <t>清邁每週末最紅的文青手作、手沖咖啡、農夫有機美食與手工藝</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>尼曼巷弄</t>
+          <t>週六日 06:00 ~ 13:00 限定</t>
         </is>
       </c>
     </row>
@@ -4293,27 +4293,27 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Kiti Panit (百年紅木老宅美饌)</t>
+          <t>瘋狂大碗麵 (Crazy Noodle)</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>米其林推薦美饌</t>
+          <t>特色平價小吃</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>1888年紅木百年老宅、米其林推薦經典烤芒果糯米飯與高檔泰菜</t>
+          <t>浮誇巨型海鮮與巨型豬肋排泰式酸辣麵碗、自選湯頭麵條</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>需預約</t>
+          <t>尼曼巷弄</t>
         </is>
       </c>
     </row>
@@ -4328,27 +4328,27 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>白色市集 (White Market Nimman)</t>
+          <t>Kiti Panit (百年紅木老宅美饌)</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>文青手作市集</t>
+          <t>米其林推薦美饌</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>One Nimman 露天廣場每週末限定白色市集！日系文青手作飾品、編織布包、文創選物與街頭美食</t>
+          <t>1888年紅木百年老宅、米其林推薦經典烤芒果糯米飯與高檔泰菜</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>週五至週日 15:00 ~ 22:00 限定</t>
+          <t>需預約</t>
         </is>
       </c>
     </row>
@@ -4363,27 +4363,27 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>MOOH (尼曼爆漿甜甜圈)</t>
+          <t>白色市集 (White Market Nimman)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>特色甜點名店</t>
+          <t>文青手作市集</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>尼曼巷弄極簡木質小店、招牌現做草莓奶油爆漿甜甜圈</t>
+          <t>One Nimman 露天廣場每週末限定白色市集！日系文青手作飾品、編織布包、文創選物與街頭美食</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>0.5 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>售完為止</t>
+          <t>週五至週日 15:00 ~ 22:00 限定</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Cheevit Cheeva (奇維奇娃冰品)</t>
+          <t>MOOH (尼曼爆漿甜甜圈)</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4408,17 +4408,17 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>清邁爆款泰式鹹蛋黃椰香雪花冰、芒果糯米冰淇淋</t>
+          <t>尼曼巷弄極簡木質小店、招牌現做草莓奶油爆漿甜甜圈</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>0.5 小時</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>尼曼熱門冰品店</t>
+          <t>售完為止</t>
         </is>
       </c>
     </row>
@@ -4433,27 +4433,27 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>7 Senses Gelato (義式手工冰淇淋)</t>
+          <t>Cheevit Cheeva (奇維奇娃冰品)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>特色甜點/手工冰淇淋</t>
+          <t>特色甜點名店</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>尼曼11巷超人氣手工義式冰淇淋！義大利主廚特調、濃郁開心果、純素與多種無乳糖口味</t>
+          <t>清邁爆款泰式鹹蛋黃椰香雪花冰、芒果糯米冰淇淋</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>0.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>尼曼 11 巷</t>
+          <t>尼曼熱門冰品店</t>
         </is>
       </c>
     </row>
@@ -4468,27 +4468,27 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>清大前門夜市 (Kad Malin Market)</t>
+          <t>7 Senses Gelato (義式手工冰淇淋)</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>學生平價夜市</t>
+          <t>特色甜點/手工冰淇淋</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>清邁大學前門超平價學生夜市、日式燒肉、衣服鞋包採買</t>
+          <t>尼曼11巷超人氣手工義式冰淇淋！義大利主廚特調、濃郁開心果、純素與多種無乳糖口味</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>0.5 小時</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>晚上熱鬧</t>
+          <t>尼曼 11 巷</t>
         </is>
       </c>
     </row>
@@ -4503,27 +4503,27 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>清大後門美食街 (Suthep Road Night Market)</t>
+          <t>清大前門夜市 (Kad Malin Market)</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>平價小吃街</t>
+          <t>學生平價夜市</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>清大後門沿街泰式小吃、現榨果汁、燕窩與泰國燒烤</t>
+          <t>清邁大學前門超平價學生夜市、日式燒肉、衣服鞋包採買</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>傍晚學生人潮</t>
+          <t>晚上熱鬧</t>
         </is>
       </c>
     </row>
@@ -4538,27 +4538,27 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Grandma's Home 泰菜廚藝學校</t>
+          <t>清大後門美食街 (Suthep Road Night Market)</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>泰菜手作體驗</t>
+          <t>平價小吃街</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>阿勛熱門推薦！農場採集食材、做芒果糯米飯與泰式炒河粉</t>
+          <t>清大後門沿街泰式小吃、現榨果汁、燕窩與泰國燒烤</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>半天</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>含飯店接送</t>
+          <t>傍晚學生人潮</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Zabb E Lee 有機農場烹飪課</t>
+          <t>Grandma's Home 泰菜廚藝學校</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>有機花園採摘香草、親手做冬陰功與泰式咖哩醬</t>
+          <t>阿勛熱門推薦！農場採集食材、做芒果糯米飯與泰式炒河粉</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -4593,42 +4593,42 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>小班制教學</t>
+          <t>含飯店接送</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>5_素貼山與悟孟寺藝文區</t>
+          <t>4_尼曼潮流區與清大商圈</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Pun Pun Organic Temple Rest (阿班有機素食)</t>
+          <t>Zabb E Lee 有機農場烹飪課</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>素食/純素餐廳</t>
+          <t>泰菜手作體驗</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>悟孟寺古森林樹蔭下有機農場蔬食、天然泰式有機素咖哩與糙米飯</t>
+          <t>有機花園採摘香草、親手做冬陰功與泰式咖哩醬</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>半天</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>悟孟寺內最受歡迎素食</t>
+          <t>小班制教學</t>
         </is>
       </c>
     </row>
@@ -4643,27 +4643,27 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>素貼山雙龍寺 (Wat Phra That Doi Suthep)</t>
+          <t>Pun Pun Organic Temple Rest (阿班有機素食)</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>古蹟/寺廟聖地</t>
+          <t>素食/純素餐廳</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>清邁指標聖地！24K 金黃大佛塔、306階納迦雙龍階梯、市區俯瞰</t>
+          <t>悟孟寺古森林樹蔭下有機農場蔬食、天然泰式有機素咖哩與糙米飯</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>可坐纜車或爬階梯</t>
+          <t>悟孟寺內最受歡迎素食</t>
         </is>
       </c>
     </row>
@@ -4678,27 +4678,27 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>蒲屏皇宮 (Bhubing Palace)</t>
+          <t>素貼山雙龍寺 (Wat Phra That Doi Suthep)</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>皇室花園</t>
+          <t>古蹟/寺廟聖地</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>泰國皇室避暑行宮、四季花卉公園與高山玫瑰園</t>
+          <t>清邁指標聖地！24K 金黃大佛塔、306階納迦雙龍階梯、市區俯瞰</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>素貼山更高處</t>
+          <t>可坐纜車或爬階梯</t>
         </is>
       </c>
     </row>
@@ -4713,17 +4713,17 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>悟孟寺 (Wat Umong)</t>
+          <t>蒲屏皇宮 (Bhubing Palace)</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>古蹟/森林寺廟</t>
+          <t>皇室花園</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>700年森林地道古寺、湖畔餵魚與苔蘚佛像秘境</t>
+          <t>泰國皇室避暑行宮、四季花卉公園與高山玫瑰園</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>氣氛極寧靜</t>
+          <t>素貼山更高處</t>
         </is>
       </c>
     </row>
@@ -4748,17 +4748,17 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>No.39 Cafe (湖畔小木屋咖啡館)</t>
+          <t>悟孟寺 (Wat Umong)</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>爆款網美咖啡</t>
+          <t>古蹟/森林寺廟</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>夢幻藍綠色水池、滑梯小木屋與露天草地音樂咖啡、小木屋打卡</t>
+          <t>700年森林地道古寺、湖畔餵魚與苔蘚佛像秘境</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>悟孟寺旁必去打卡熱點</t>
+          <t>氣氛極寧靜</t>
         </is>
       </c>
     </row>
@@ -4783,27 +4783,27 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Baan Kang Wat 森林手作藝術村</t>
+          <t>No.39 Cafe (湖畔小木屋咖啡館)</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>藝文體驗/手作</t>
+          <t>爆款網美咖啡</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>泥土小路、木造手作工作坊、陶藝體驗與獨立書店</t>
+          <t>夢幻藍綠色水池、滑梯小木屋與露天草地音樂咖啡、小木屋打卡</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>週一公休</t>
+          <t>悟孟寺旁必去打卡熱點</t>
         </is>
       </c>
     </row>
@@ -4818,27 +4818,27 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Early Owls Cafe (草地大樹咖啡)</t>
+          <t>Baan Kang Wat 森林手作藝術村</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>網美野餐咖啡</t>
+          <t>藝文體驗/手作</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>超大片天然綠色草地、溪流與大樹野餐椅、天然愜意氛圍</t>
+          <t>泥土小路、木造手作工作坊、陶藝體驗與獨立書店</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>適合放空野餐</t>
+          <t>週一公休</t>
         </is>
       </c>
     </row>
@@ -4853,17 +4853,17 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Nana Jungle (森林麵包市集)</t>
+          <t>Early Owls Cafe (草地大樹咖啡)</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>特色美饌市集</t>
+          <t>網美野餐咖啡</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>每週六限定！森林裡排隊搶購的現烤歐式法棍與可頌</t>
+          <t>超大片天然綠色草地、溪流與大樹野餐椅、天然愜意氛圍</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>週六早晨 08:00 限定</t>
+          <t>適合放空野餐</t>
         </is>
       </c>
     </row>
@@ -4888,27 +4888,27 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>界遙寺 (Wat Jet Yod)</t>
+          <t>Nana Jungle (森林麵包市集)</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>古蹟/寺廟</t>
+          <t>特色美饌市集</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>印度菩提伽耶風格七頂塔、平靜古木森林寺廟</t>
+          <t>每週六限定！森林裡排隊搶購的現烤歐式法棍與可頌</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>清邁超級古寺</t>
+          <t>週六早晨 08:00 限定</t>
         </is>
       </c>
     </row>
@@ -4923,17 +4923,17 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Blue Coffee at Agriculture CMU</t>
+          <t>界遙寺 (Wat Jet Yod)</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>清大校園咖啡</t>
+          <t>古蹟/寺廟</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>清邁大學農學院大片落地窗草地咖啡、超極簡景觀與平價咖啡</t>
+          <t>印度菩提伽耶風格七頂塔、平靜古木森林寺廟</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>清大校園內</t>
+          <t>清邁超級古寺</t>
         </is>
       </c>
     </row>
@@ -4958,27 +4958,27 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>帕拉寺 (Wat Pha Lat)</t>
+          <t>Blue Coffee at Agriculture CMU</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>森林溪流古寺</t>
+          <t>清大校園咖啡</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>隱匿於素貼山半山腰森林中的古老溪流寺廟、苔蘚石佛與瀑布</t>
+          <t>清邁大學農學院大片落地窗草地咖啡、超極簡景觀與平價咖啡</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>雙龍寺途經秘境</t>
+          <t>清大校園內</t>
         </is>
       </c>
     </row>
@@ -4993,27 +4993,27 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>素貼山觀景台 (Doi Suthep Viewpoint)</t>
+          <t>帕拉寺 (Wat Pha Lat)</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>高山景觀平台</t>
+          <t>森林溪流古寺</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>半山腰無遮蔽觀景台、俯瞰整座清邁城區與機場跑道</t>
+          <t>隱匿於素貼山半山腰森林中的古老溪流寺廟、苔蘚石佛與瀑布</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>0.5 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>看夜景首選</t>
+          <t>雙龍寺途經秘境</t>
         </is>
       </c>
     </row>
@@ -5028,27 +5028,27 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>坤昌阡 (Khun Chang Kian 櫻花谷)</t>
+          <t>素貼山觀景台 (Doi Suthep Viewpoint)</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>高山櫻花景觀</t>
+          <t>高山景觀平台</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>素貼山頂苗族部落、每年1-2月盛開的泰國高山野櫻花</t>
+          <t>半山腰無遮蔽觀景台、俯瞰整座清邁城區與機場跑道</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>0.5 小時</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>賞櫻季首選</t>
+          <t>看夜景首選</t>
         </is>
       </c>
     </row>
@@ -5063,27 +5063,27 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Doi Chaang Coffee Doi Suthep</t>
+          <t>坤昌阡 (Khun Chang Kian 櫻花谷)</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>高山景觀咖啡</t>
+          <t>高山櫻花景觀</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>素貼山半山腰景觀平台、品嚐泰北知名象山高山精品咖啡</t>
+          <t>素貼山頂苗族部落、每年1-2月盛開的泰國高山野櫻花</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>山景第一排</t>
+          <t>賞櫻季首選</t>
         </is>
       </c>
     </row>
@@ -5098,27 +5098,27 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>僧侶步道 (Monk's Trail)</t>
+          <t>Doi Chaang Coffee Doi Suthep</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>森林徒步步道</t>
+          <t>高山景觀咖啡</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>綁著橘色僧袍樹木指引的清邁最經典森林徒步路線</t>
+          <t>素貼山半山腰景觀平台、品嚐泰北知名象山高山精品咖啡</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>直通帕拉寺</t>
+          <t>山景第一排</t>
         </is>
       </c>
     </row>
@@ -5133,27 +5133,27 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>清邁大學靜心湖 (Ang Kaew CMU)</t>
+          <t>僧侶步道 (Monk's Trail)</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>校園水岸景觀</t>
+          <t>森林徒步步道</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>清大湖畔大片草地、素貼山倒影與傍晚散步打卡勝地</t>
+          <t>綁著橘色僧袍樹木指引的清邁最經典森林徒步路線</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>傍晚最熱門</t>
+          <t>直通帕拉寺</t>
         </is>
       </c>
     </row>
@@ -5168,17 +5168,17 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>清邁國家博物館 (Chiang Mai National Museum)</t>
+          <t>清邁大學靜心湖 (Ang Kaew CMU)</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>歷史博物館</t>
+          <t>校園水岸景觀</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>界遙寺旁、展示蘭納王朝珍貴佛像、文物與王室金飾</t>
+          <t>清大湖畔大片草地、素貼山倒影與傍晚散步打卡勝地</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -5188,42 +5188,42 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>歷史控必去</t>
+          <t>傍晚最熱門</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>6_清邁東郊湄康蓬區</t>
+          <t>5_素貼山與悟孟寺藝文區</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Meena Rice Based Cuisine (五色米飯)</t>
+          <t>清邁國家博物館 (Chiang Mai National Museum)</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>米其林必比登餐廳</t>
+          <t>歷史博物館</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>米其林必比登推薦！清邁東郊花園水池、招牌五彩金字塔米飯與精緻泰菜</t>
+          <t>界遙寺旁、展示蘭納王朝珍貴佛像、文物與王室金飾</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>三甘攀區名店</t>
+          <t>歷史控必去</t>
         </is>
       </c>
     </row>
@@ -5238,17 +5238,17 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>The Giant Chiang Mai (大樹咖啡館)</t>
+          <t>Meena Rice Based Cuisine (五色米飯)</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>網美懸空咖啡</t>
+          <t>米其林必比登餐廳</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>建於千年巨樹冠頂！懸空木棧道、吊橋與高空滑索 (Zipline)</t>
+          <t>米其林必比登推薦！清邁東郊花園水池、招牌五彩金字塔米飯與精緻泰菜</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>位於梅翁縣山頂</t>
+          <t>三甘攀區名店</t>
         </is>
       </c>
     </row>
@@ -5273,27 +5273,27 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>羅賓帕薩樹屋度假村 (Rabeang Pasak Treehouse)</t>
+          <t>The Giant Chiang Mai (大樹咖啡館)</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>爆款高山樹屋咖啡</t>
+          <t>網美懸空咖啡</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>清邁最經典高山樹屋！高聳樹冠木造小屋、森林步道與樹屋咖啡館</t>
+          <t>建於千年巨樹冠頂！懸空木棧道、吊橋與高空滑索 (Zipline)</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>三甘攀/梅翁高山秘境</t>
+          <t>位於梅翁縣山頂</t>
         </is>
       </c>
     </row>
@@ -5308,27 +5308,27 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>湄康蓬古村 (Mae Kampong)</t>
+          <t>羅賓帕薩樹屋度假村 (Rabeang Pasak Treehouse)</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>百年古村秘境</t>
+          <t>爆款高山樹屋咖啡</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>沿著溪流與山谷建造的木造高腳屋部落、山溪瀑布、高山茶咖啡</t>
+          <t>清邁最經典高山樹屋！高聳樹冠木造小屋、森林步道與樹屋咖啡館</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>3 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>清邁最熱門包車山村</t>
+          <t>三甘攀/梅翁高山秘境</t>
         </is>
       </c>
     </row>
@@ -5343,27 +5343,27 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>湄康蓬瀑布 (Mae Kampong Waterfall)</t>
+          <t>湄康蓬古村 (Mae Kampong)</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>自然瀑布</t>
+          <t>百年古村秘境</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>古村頂端七層山谷瀑布、涼爽森林步道</t>
+          <t>沿著溪流與山谷建造的木造高腳屋部落、山溪瀑布、高山茶咖啡</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>3 小時</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>古村上方</t>
+          <t>清邁最熱門包車山村</t>
         </is>
       </c>
     </row>
@@ -5378,27 +5378,27 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Chom Nok Chom Mai (古村俯瞰咖啡)</t>
+          <t>湄康蓬瀑布 (Mae Kampong Waterfall)</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>山谷觀景咖啡</t>
+          <t>自然瀑布</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>位於湄康蓬村頂木造平台、俯瞰整座山谷部落與雲霧</t>
+          <t>古村頂端七層山谷瀑布、涼爽森林步道</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>拍古村全景最佳點</t>
+          <t>古村上方</t>
         </is>
       </c>
     </row>
@@ -5413,17 +5413,17 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Ted's Army Cafe (森林溪流咖啡)</t>
+          <t>Chom Nok Chom Mai (古村俯瞰咖啡)</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>溪流木屋咖啡</t>
+          <t>山谷觀景咖啡</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>建於湄康蓬森林溪流旁、聽著水聲喝咖啡與烤吐司</t>
+          <t>位於湄康蓬村頂木造平台、俯瞰整座山谷部落與雲霧</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>古村溪邊</t>
+          <t>拍古村全景最佳點</t>
         </is>
       </c>
     </row>
@@ -5448,27 +5448,27 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Flying Squirrels 叢林滑索</t>
+          <t>Ted's Army Cafe (森林溪流咖啡)</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>戶外叢林滑索</t>
+          <t>溪流木屋咖啡</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>森林叢林飛躍滑索 (Ziplines)、樹頂走廊空中體驗</t>
+          <t>建於湄康蓬森林溪流旁、聽著水聲喝咖啡與烤吐司</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>3 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>適合喜愛冒險遊客</t>
+          <t>古村溪邊</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Skyline Adventure 高空滑索</t>
+          <t>Flying Squirrels 叢林滑索</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -5493,17 +5493,17 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>泰國最長高空滑索線路之一、飛越高山峽谷雨林</t>
+          <t>森林叢林飛躍滑索 (Ziplines)、樹頂走廊空中體驗</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>3.5 小時</t>
+          <t>3 小時</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>包含飯店接送</t>
+          <t>適合喜愛冒險遊客</t>
         </is>
       </c>
     </row>
@@ -5518,27 +5518,27 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>三甘攀天然溫泉 (San Kamphaeng Springs)</t>
+          <t>Skyline Adventure 高空滑索</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>天然溫泉公園</t>
+          <t>戶外叢林滑索</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>高壓噴湧溫泉水柱、露天泡腳池與煮溫泉蛋體驗</t>
+          <t>泰國最長高空滑索線路之一、飛越高山峽谷雨林</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>3.5 小時</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>回程途經中途站</t>
+          <t>包含飯店接送</t>
         </is>
       </c>
     </row>
@@ -5553,17 +5553,17 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>博桑手作紙傘村 (Bo Sang Village)</t>
+          <t>三甘攀天然溫泉 (San Kamphaeng Springs)</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>傳統手作村</t>
+          <t>天然溫泉公園</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>百年彩繪竹骨紙傘手作村、師傅現場在手機殼/包包彩繪</t>
+          <t>高壓噴湧溫泉水柱、露天泡腳池與煮溫泉蛋體驗</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>三甘攀路上</t>
+          <t>回程途經中途站</t>
         </is>
       </c>
     </row>
@@ -5588,27 +5588,27 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>博桑手工紙傘文創館</t>
+          <t>博桑手作紙傘村 (Bo Sang Village)</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>文化體驗</t>
+          <t>傳統手作村</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>彩繪紙傘 DIY 體驗、泰國傳統桑皮紙製作展示</t>
+          <t>百年彩繪竹骨紙傘手作村、師傅現場在手機殼/包包彩繪</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>適合親子 DIY</t>
+          <t>三甘攀路上</t>
         </is>
       </c>
     </row>
@@ -5623,17 +5623,17 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>雙溪谷地觀景台 (Doi Saket)</t>
+          <t>博桑手工紙傘文創館</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>高山觀景台</t>
+          <t>文化體驗</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>位於梅翁與雙溪山脈交界、俯瞰水庫與高山谷地</t>
+          <t>彩繪紙傘 DIY 體驗、泰國傳統桑皮紙製作展示</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>公路景觀點</t>
+          <t>適合親子 DIY</t>
         </is>
       </c>
     </row>
@@ -5658,27 +5658,27 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>The Giant Zipline (大樹高空滑索)</t>
+          <t>雙溪谷地觀景台 (Doi Saket)</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>樹頂高空體驗</t>
+          <t>高山觀景台</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>從千年大樹冠頂直接滑向對面山谷的單線體驗</t>
+          <t>位於梅翁與雙溪山脈交界、俯瞰水庫與高山谷地</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>0.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>大樹咖啡館內</t>
+          <t>公路景觀點</t>
         </is>
       </c>
     </row>
@@ -5693,27 +5693,27 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>綠野仙蹤溫泉度假村 (San Kamphaeng Hot Spring Resort)</t>
+          <t>The Giant Zipline (大樹高空滑索)</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>溫泉休閒</t>
+          <t>樹頂高空體驗</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>天然礦物溫泉個人湯屋、露天溫泉游泳池與日式足湯</t>
+          <t>從千年大樹冠頂直接滑向對面山谷的單線體驗</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>0.5 小時</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>三甘攀山腳</t>
+          <t>大樹咖啡館內</t>
         </is>
       </c>
     </row>
@@ -5728,52 +5728,52 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Baan Suan Phak (泰北蔬菜園)</t>
+          <t>綠野仙蹤溫泉度假村 (San Kamphaeng Hot Spring Resort)</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>米其林推薦美饌</t>
+          <t>溫泉休閒</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>米其林推薦！天然農場有機蔬果料理、泰式炸魚與鮮採沙拉</t>
+          <t>天然礦物溫泉個人湯屋、露天溫泉游泳池與日式足湯</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>東郊綠意庭園</t>
+          <t>三甘攀山腳</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>8_清邁南郊杭東與美王休閒區</t>
+          <t>6_清邁東郊湄康蓬區</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Pure Vegan Heaven Chiang Mai</t>
+          <t>Baan Suan Phak (泰北蔬菜園)</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>素食/純素餐廳</t>
+          <t>米其林推薦美饌</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>杭東熱門爆款純素天堂餐廳！純素墨西哥塔可、彩虹水果碗與純素起司通心粉</t>
+          <t>米其林推薦！天然農場有機蔬果料理、泰式炸魚與鮮採沙拉</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -5783,42 +5783,42 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>杭東區必去純素</t>
+          <t>東郊綠意庭園</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>7_清邁北郊梅林山谷區</t>
+          <t>8_清邁南郊杭東與美王休閒區</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>梅莎七層瀑布 (Mae Sa Waterfall)</t>
+          <t>Pure Vegan Heaven Chiang Mai</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>自然瀑布森林</t>
+          <t>素食/純素餐廳</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>梅林區最著名七層階梯式高山瀑布、清涼溪流與森林芬多精步道</t>
+          <t>杭東熱門爆款純素天堂餐廳！純素墨西哥塔可、彩虹水果碗與純素起司通心粉</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>梅林區核心自然景點</t>
+          <t>杭東區必去純素</t>
         </is>
       </c>
     </row>
@@ -5833,17 +5833,17 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>清邁皇家陸軍實彈射擊場 (Mae Rim Shooting Club)</t>
+          <t>梅莎七層瀑布 (Mae Sa Waterfall)</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>極限冒險體驗</t>
+          <t>自然瀑布森林</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>泰國皇家陸軍正規實彈射擊靶場！霰彈槍、9mm 手槍、AR15 步槍真槍實彈體驗與教練指導</t>
+          <t>梅林區最著名七層階梯式高山瀑布、清涼溪流與森林芬多精步道</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>梅林區熱門冒險行程</t>
+          <t>梅林區核心自然景點</t>
         </is>
       </c>
     </row>
@@ -5868,62 +5868,62 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>清邁 ATV 越野車冒險 (Chiang Mai ATV Off-Road)</t>
+          <t>清邁皇家陸軍實彈射擊場 (Mae Rim Shooting Club)</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>戶外極限體驗</t>
+          <t>極限冒險體驗</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>駕駛四輪全地形 ATV 越野車穿梭梅林山谷泥地、溪流與泥濘步道</t>
+          <t>泰國皇家陸軍正規實彈射擊靶場！霰彈槍、9mm 手槍、AR15 步槍真槍實彈體驗與教練指導</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>含安全裝備與教練</t>
+          <t>梅林區熱門冒險行程</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>8_清邁南郊杭東與美王休閒區</t>
+          <t>7_清邁北郊梅林山谷區</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>清邁 Paramotor 輕型動力傘 (Paramotor Flight)</t>
+          <t>清邁 ATV 越野車冒險 (Chiang Mai ATV Off-Road)</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>高空飛行體驗</t>
+          <t>戶外極限體驗</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>專業飛行員帶領乘坐動力飛行傘升空、鳥瞰清邁日出與稻田全景</t>
+          <t>駕駛四輪全地形 ATV 越野車穿梭梅林山谷泥地、溪流與泥濘步道</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>清晨日出時段</t>
+          <t>含安全裝備與教練</t>
         </is>
       </c>
     </row>
@@ -5938,27 +5938,27 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Ajarn Saiyud's Kitchen (Saiyud 皇家宮廷菜)</t>
+          <t>清邁 Paramotor 輕型動力傘 (Paramotor Flight)</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>米其林必比登餐廳</t>
+          <t>高空飛行體驗</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>米其林必比登推薦！清邁最頂級皇家雕花宮廷菜、泰式蝶豆花雕花點心</t>
+          <t>專業飛行員帶領乘坐動力飛行傘升空、鳥瞰清邁日出與稻田全景</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>需提前一個月預約</t>
+          <t>清晨日出時段</t>
         </is>
       </c>
     </row>
@@ -5973,27 +5973,27 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Chom Cafe &amp; Restaurant (熱帶雨林瀑布咖啡)</t>
+          <t>Ajarn Saiyud's Kitchen (Saiyud 皇家宮廷菜)</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>熱帶雨林瀑布咖啡</t>
+          <t>米其林必比登餐廳</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>清邁最夢幻熱帶雨林花園！自然水霧、人造瀑布與綠苔秘境景觀餐廳</t>
+          <t>米其林必比登推薦！清邁最頂級皇家雕花宮廷菜、泰式蝶豆花雕花點心</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>建議預約免排隊</t>
+          <t>需提前一個月預約</t>
         </is>
       </c>
     </row>
@@ -6008,17 +6008,17 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Carp Café (錦鯉咖啡館)</t>
+          <t>Chom Cafe &amp; Restaurant (熱帶雨林瀑布咖啡)</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>爆款網美咖啡</t>
+          <t>熱帶雨林瀑布咖啡</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>數萬條絢麗日本錦鯉悠游水池、日式霧氣庭園與日式餐點甜點</t>
+          <t>清邁最夢幻熱帶雨林花園！自然水霧、人造瀑布與綠苔秘境景觀餐廳</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>杭東區打卡首選</t>
+          <t>建議預約免排隊</t>
         </is>
       </c>
     </row>
@@ -6043,27 +6043,27 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>黑森林景觀餐廳 (Khaomao-Khaofang)</t>
+          <t>Carp Café (錦鯉咖啡館)</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>爆款景觀餐廳</t>
+          <t>爆款網美咖啡</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>被譽為世界前十大森林系餐廳！巨型室內瀑布、流泉與花卉宴會</t>
+          <t>數萬條絢麗日本錦鯉悠游水池、日式霧氣庭園與日式餐點甜點</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>杭東最熱門景觀餐廳</t>
+          <t>杭東區打卡首選</t>
         </is>
       </c>
     </row>
@@ -6078,97 +6078,97 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>大象朋友飯店 / Chai Lai Orchid</t>
+          <t>黑森林景觀餐廳 (Khaomao-Khaofang)</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>爆款大象體驗</t>
+          <t>爆款景觀餐廳</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>IG爆紅大象朋友飯店！大象早晨叩窗敲門、大象溪流沐浴與竹伐漂流</t>
+          <t>被譽為世界前十大森林系餐廳！巨型室內瀑布、流泉與花卉宴會</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>半天 ~ 一晚</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>美王縣爆款住宿體驗</t>
+          <t>杭東最熱門景觀餐廳</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>7_清邁北郊梅林山谷區</t>
+          <t>8_清邁南郊杭東與美王休閒區</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Elephant POOPOOPAPER Park (大象便便紙公園)</t>
+          <t>大象朋友飯店 / Chai Lai Orchid</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>親子環保手作</t>
+          <t>爆款大象體驗</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>大象糞便回收造紙主題公園！寓教於樂、手作便便紙手工書與書籤</t>
+          <t>IG爆紅大象朋友飯店！大象早晨叩窗敲門、大象溪流沐浴與竹伐漂流</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>半天 ~ 一晚</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>梅林區爆款親子景點</t>
+          <t>美王縣爆款住宿體驗</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>8_清邁南郊杭東與美王休閒區</t>
+          <t>7_清邁北郊梅林山谷區</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Elephant Nature Park (大象自然公園)</t>
+          <t>Elephant POOPOOPAPER Park (大象便便紙公園)</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>大象體驗/生態</t>
+          <t>親子環保手作</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>友善大象保護區、不騎大象、給大象洗澡餵食體驗</t>
+          <t>大象糞便回收造紙主題公園！寓教於樂、手作便便紙手工書與書籤</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>半天</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>需提前官網預約</t>
+          <t>梅林區爆款親子景點</t>
         </is>
       </c>
     </row>
@@ -6183,17 +6183,17 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Kanta Elephant Sanctuary (坎塔大象保護區)</t>
+          <t>Elephant Nature Park (大象自然公園)</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>友善大象體驗</t>
+          <t>大象體驗/生態</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>阿勛熱門推薦！穿著卡倫族服飾、製作大象營養飯糰與泥巴浴</t>
+          <t>友善大象保護區、不騎大象、給大象洗澡餵食體驗</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>不騎大象無表演</t>
+          <t>需提前官網預約</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>HugElephant (抱抱大象保護區)</t>
+          <t>Kanta Elephant Sanctuary (坎塔大象保護區)</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>美王山谷高山大象保育園區、大象溪流散步與洗澡</t>
+          <t>阿勛熱門推薦！穿著卡倫族服飾、製作大象營養飯糰與泥巴浴</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -6238,77 +6238,77 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>美王縣</t>
+          <t>不騎大象無表演</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>7_清邁北郊梅林山谷區</t>
+          <t>8_清邁南郊杭東與美王休閒區</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>梅莎大象營 (Mae Sa Elephant Camp)</t>
+          <t>HugElephant (抱抱大象保護區)</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>傳統大象營</t>
+          <t>友善大象體驗</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>清邁老牌大象園區、大象洗澡與大象餵食互動體驗</t>
+          <t>美王山谷高山大象保育園區、大象溪流散步與洗澡</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>半天</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>梅林區</t>
+          <t>美王縣</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>8_清邁南郊杭東與美王休閒區</t>
+          <t>7_清邁北郊梅林山谷區</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>清邁夜間野生動物園 (Night Safari)</t>
+          <t>梅莎大象營 (Mae Sa Elephant Camp)</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>夜間生態體驗</t>
+          <t>傳統大象營</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>乘坐開放式遊園車近距離餵食長頸鹿、斑馬與猛獸展演</t>
+          <t>清邁老牌大象園區、大象洗澡與大象餵食互動體驗</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>3 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>傍晚 18:00 入園最佳</t>
+          <t>梅林區</t>
         </is>
       </c>
     </row>
@@ -6323,27 +6323,27 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>金山寺 (Wat Phra That Doi Kham)</t>
+          <t>清邁夜間野生動物園 (Night Safari)</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>許願靈驗寺廟</t>
+          <t>夜間生態體驗</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>清邁許願最靈驗寺廟！17公尺巨型坐佛、滿山茉莉花供奉</t>
+          <t>乘坐開放式遊園車近距離餵食長頸鹿、斑馬與猛獸展演</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>3 小時</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>杭東山丘</t>
+          <t>傍晚 18:00 入園最佳</t>
         </is>
       </c>
     </row>
@@ -6358,62 +6358,62 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>皇家花園 (Royal Park Rajapruek)</t>
+          <t>金山寺 (Wat Phra That Doi Kham)</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>皇家植物園</t>
+          <t>許願靈驗寺廟</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>拉查帕皇家植物園、黃金蘭納宮殿主殿與各國展覽花園</t>
+          <t>清邁許願最靈驗寺廟！17公尺巨型坐佛、滿山茉莉花供奉</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>可搭乘園區遊覽車</t>
+          <t>杭東山丘</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>7_清邁北郊梅林山谷區</t>
+          <t>8_清邁南郊杭東與美王休閒區</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>蒙瞻山 (Mon Jam / 夢瞻山)</t>
+          <t>皇家花園 (Royal Park Rajapruek)</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>高山景觀/花海</t>
+          <t>皇家植物園</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>高山梯田花海、懸崖露營、高山木製卡丁車 (Hmong Cart)</t>
+          <t>拉查帕皇家植物園、黃金蘭納宮殿主殿與各國展覽花園</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>3 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>梅林區高山</t>
+          <t>可搭乘園區遊覽車</t>
         </is>
       </c>
     </row>
@@ -6428,27 +6428,27 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Fleur Cafe &amp; Eatery</t>
+          <t>蒙瞻山 (Mon Jam / 夢瞻山)</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>英式莊園咖啡</t>
+          <t>高山景觀/花海</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>梅林區絕美英式玫瑰花園、白色玻璃木屋與法式甜點</t>
+          <t>高山梯田花海、懸崖露營、高山木製卡丁車 (Hmong Cart)</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>3 小時</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>梅林區打卡名店</t>
+          <t>梅林區高山</t>
         </is>
       </c>
     </row>
@@ -6463,17 +6463,17 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>皇后植物園天空步道 (Queen Sirikit)</t>
+          <t>Fleur Cafe &amp; Eatery</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>植物園/空中步道</t>
+          <t>英式莊園咖啡</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>樹頂透明空中玻璃步道與巨型溫室多肉植物園</t>
+          <t>梅林區絕美英式玫瑰花園、白色玻璃木屋與法式甜點</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -6483,42 +6483,42 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>梅林區地標</t>
+          <t>梅林區打卡名店</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>8_清邁南郊杭東與美王休閒區</t>
+          <t>7_清邁北郊梅林山谷區</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>帕丘峽谷 (Pha Chor Canyon)</t>
+          <t>皇后植物園天空步道 (Queen Sirikit)</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>自然地質奇景</t>
+          <t>植物園/空中步道</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>被譽為「泰國版大峽谷」的天然地質巨石柱與峽谷奇景</t>
+          <t>樹頂透明空中玻璃步道與巨型溫室多肉植物園</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>清邁南部美王縣</t>
+          <t>梅林區地標</t>
         </is>
       </c>
     </row>
@@ -6533,17 +6533,17 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>惠登套湖 (Huay Tung Tao Lake)</t>
+          <t>帕丘峽谷 (Pha Chor Canyon)</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>湖畔農場景觀</t>
+          <t>自然地質奇景</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>巨型草編大象金剛家族雕塑、湖畔涼亭泰菜與水上腳踏船</t>
+          <t>被譽為「泰國版大峽谷」的天然地質巨石柱與峽谷奇景</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>素貼山腳北側</t>
+          <t>清邁南部美王縣</t>
         </is>
       </c>
     </row>
@@ -6568,27 +6568,27 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>惠登套湖水中樹 (Huay Tung Tao Water Tree)</t>
+          <t>惠登套湖 (Huay Tung Tao Lake)</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>湖畔倒影打卡點</t>
+          <t>湖畔農場景觀</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>清邁爆款景觀！惠登套湖水中矗立的孤獨樹木與草編金剛背景倒影</t>
+          <t>巨型草編大象金剛家族雕塑、湖畔涼亭泰菜與水上腳踏船</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>惠登套湖內</t>
+          <t>素貼山腳北側</t>
         </is>
       </c>
     </row>
@@ -6603,27 +6603,27 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>清邁大峽谷水上樂園 (Grand Canyon)</t>
+          <t>惠登套湖水中樹 (Huay Tung Tao Water Tree)</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>水上戶外樂園</t>
+          <t>湖畔倒影打卡點</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>採石場天然巨岩水上樂園、高空跳水、充氣水上障礙賽與划艇</t>
+          <t>清邁爆款景觀！惠登套湖水中矗立的孤獨樹木與草編金剛背景倒影</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>3 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>杭東區戶外名店</t>
+          <t>惠登套湖內</t>
         </is>
       </c>
     </row>
@@ -6638,62 +6638,62 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>美王河竹伐漂流 (Mae Wang Bamboo Rafting)</t>
+          <t>清邁大峽谷水上樂園 (Grand Canyon)</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>戶外溪流體驗</t>
+          <t>水上戶外樂園</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>傳統竹筏順著清澈美王河漂流、沿岸清涼溪水與野生大象</t>
+          <t>採石場天然巨岩水上樂園、高空跳水、充氣水上障礙賽與划艇</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>3 小時</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>美王縣爆款</t>
+          <t>杭東區戶外名店</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>7_清邁北郊梅林山谷區</t>
+          <t>8_清邁南郊杭東與美王休閒區</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Pongyang Jungle Coaster &amp; Zipline</t>
+          <t>美王河竹伐漂流 (Mae Wang Bamboo Rafting)</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>戶外極限體驗</t>
+          <t>戶外溪流體驗</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>梅林高山森林過山車 (Jungle Coaster)、高空自行車與滑索</t>
+          <t>傳統竹筏順著清澈美王河漂流、沿岸清涼溪水與野生大象</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>梅林區爆款</t>
+          <t>美王縣爆款</t>
         </is>
       </c>
     </row>
@@ -6708,27 +6708,27 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Eagle Track Zipline (鷹軌叢林滑索)</t>
+          <t>Pongyang Jungle Coaster &amp; Zipline</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>戶外叢林滑索</t>
+          <t>戶外極限體驗</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>阿勛精選推薦！穿梭梯田、瀑布與森林的冒險空中索道</t>
+          <t>梅林高山森林過山車 (Jungle Coaster)、高空自行車與滑索</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>3 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>梅林區</t>
+          <t>梅林區爆款</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Dragon Flight Zipline (飛龍高空滑索)</t>
+          <t>Eagle Track Zipline (鷹軌叢林滑索)</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>包含泰國頂級樹頂過山車與多道高空飛行平台</t>
+          <t>阿勛精選推薦！穿梭梯田、瀑布與森林的冒險空中索道</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>3.5 小時</t>
+          <t>3 小時</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -6769,71 +6769,71 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>8_清邁南郊杭東與美王休閒區</t>
+          <t>7_清邁北郊梅林山谷區</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>木雕工藝村 (Baan Tawai)</t>
+          <t>Dragon Flight Zipline (飛龍高空滑索)</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>傳統手作工藝</t>
+          <t>戶外叢林滑索</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>清邁最大傳統木雕手工藝批發村、精雕木家具與裝飾</t>
+          <t>包含泰國頂級樹頂過山車與多道高空飛行平台</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>3.5 小時</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>杭東區古老村落</t>
+          <t>梅林區</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>7_清邁北郊梅林山谷區</t>
+          <t>8_清邁南郊杭東與美王休閒區</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>老虎王國 (Tiger Kingdom Chiang Mai)</t>
+          <t>木雕工藝村 (Baan Tawai)</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>野生動物體驗</t>
+          <t>傳統手作工藝</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>近距離撫摸與合照大老虎與小老虎、專業飼養員陪同</t>
+          <t>清邁最大傳統木雕手工藝批發村、精雕木家具與裝飾</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>梅林區名店</t>
+          <t>杭東區古老村落</t>
         </is>
       </c>
     </row>
@@ -6848,97 +6848,97 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>綠谷高爾夫球俱樂部 (Summit Green Valley)</t>
+          <t>老虎王國 (Tiger Kingdom Chiang Mai)</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>高爾夫休閒</t>
+          <t>野生動物體驗</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>18洞國際錦標賽等級高爾夫球場、壯麗山景倒影</t>
+          <t>近距離撫摸與合照大老虎與小老虎、專業飼養員陪同</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>半天</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>梅林區名球場</t>
+          <t>梅林區名店</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>8_清邁南郊杭東與美王休閒區</t>
+          <t>7_清邁北郊梅林山谷區</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Khao Hom Muang Phrae (米其林帕府風味菜)</t>
+          <t>綠谷高爾夫球俱樂部 (Summit Green Valley)</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>米其林推薦餐廳</t>
+          <t>高爾夫休閒</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>米其林推薦！泰北帕府古法泰菜、香草烤豬肉與炸魚皮</t>
+          <t>18洞國際錦標賽等級高爾夫球場、壯麗山景倒影</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>半天</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>杭東區庭園</t>
+          <t>梅林區名球場</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>9_因他農山國家公園區</t>
+          <t>8_清邁南郊杭東與美王休閒區</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>因他農山頂 (Doi Inthanon Peak)</t>
+          <t>Khao Hom Muang Phrae (米其林帕府風味菜)</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>國家公園/自然</t>
+          <t>米其林推薦餐廳</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>泰國最高峰 (2565m)、冷溫帶霧林與 Angel Walk 木棧道健行</t>
+          <t>米其林推薦！泰北帕府古法泰菜、香草烤豬肉與炸魚皮</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>全年氣溫涼爽(10-15度)</t>
+          <t>杭東區庭園</t>
         </is>
       </c>
     </row>
@@ -6953,27 +6953,27 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>國王王后雙塔 (King &amp; Queen Pagodas)</t>
+          <t>因他農山頂 (Doi Inthanon Peak)</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>皇家地標/花園</t>
+          <t>國家公園/自然</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>壯麗高山皇家花園雙塔、俯瞰雲海與紫色彩虹花海</t>
+          <t>泰國最高峰 (2565m)、冷溫帶霧林與 Angel Walk 木棧道健行</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>有扶手電梯可上塔</t>
+          <t>全年氣溫涼爽(10-15度)</t>
         </is>
       </c>
     </row>
@@ -6988,27 +6988,27 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>瓦吉拉坦瀑布 (Wachirathan Waterfall)</t>
+          <t>國王王后雙塔 (King &amp; Queen Pagodas)</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>自然瀑布</t>
+          <t>皇家地標/花園</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>氣勢磅礡巨型瀑布、水霧彩虹打卡點與山谷咖啡休息站</t>
+          <t>壯麗高山皇家花園雙塔、俯瞰雲海與紫色彩虹花海</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>山腳下必停留站</t>
+          <t>有扶手電梯可上塔</t>
         </is>
       </c>
     </row>
@@ -7023,27 +7023,27 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Mae Ya 瀑布 (Mae Ya Waterfall)</t>
+          <t>瓦吉拉坦瀑布 (Wachirathan Waterfall)</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>泰國第一大瀑布</t>
+          <t>自然瀑布</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>清邁最壯觀多層次階梯式巨型瀑布、宛如水簾洞</t>
+          <t>氣勢磅礡巨型瀑布、水霧彩虹打卡點與山谷咖啡休息站</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>因他農山麓必去</t>
+          <t>山腳下必停留站</t>
         </is>
       </c>
     </row>
@@ -7058,27 +7058,27 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Sirithan 瀑布 (Mae Klang)</t>
+          <t>Mae Ya 瀑布 (Mae Ya Waterfall)</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>自然瀑布</t>
+          <t>泰國第一大瀑布</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>山谷深處雙層飛瀑、森林芬多精健行步道</t>
+          <t>清邁最壯觀多層次階梯式巨型瀑布、宛如水簾洞</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>國家公園內</t>
+          <t>因他農山麓必去</t>
         </is>
       </c>
     </row>
@@ -7093,27 +7093,27 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Kew Mae Pan 雲海步道</t>
+          <t>Sirithan 瀑布 (Mae Klang)</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>高山健行步道</t>
+          <t>自然瀑布</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>清邁最美雲海健行步道、高山杜鵑花與懸崖景觀平台</t>
+          <t>山谷深處雙層飛瀑、森林芬多精健行步道</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>每年11月至5月開放</t>
+          <t>國家公園內</t>
         </is>
       </c>
     </row>
@@ -7128,27 +7128,27 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>坤旺皇家農業中心 (Khun Wang 櫻花谷)</t>
+          <t>Kew Mae Pan 雲海步道</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>高山櫻花勝地</t>
+          <t>高山健行步道</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>因他農山高山櫻花隧道、寒帶水果與高山茶園</t>
+          <t>清邁最美雲海健行步道、高山杜鵑花與懸崖景觀平台</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>每年1-2月爆發盛開</t>
+          <t>每年11月至5月開放</t>
         </is>
       </c>
     </row>
@@ -7163,27 +7163,27 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Ban Pa Pong Piang 梯田梯稻觀景台</t>
+          <t>坤旺皇家農業中心 (Khun Wang 櫻花谷)</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>梯田絕景</t>
+          <t>高山櫻花勝地</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>被譽為泰國最美高山水稻梯田村落、夕陽與稻浪倒影</t>
+          <t>因他農山高山櫻花隧道、寒帶水果與高山茶園</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>3 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>每年9-11月黃金稻浪</t>
+          <t>每年1-2月爆發盛開</t>
         </is>
       </c>
     </row>
@@ -7198,27 +7198,27 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>Ang Ka 冷溫帶高山步道 (Ang Ka Nature Trail)</t>
+          <t>Ban Pa Pong Piang 梯田梯稻觀景台</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>高山苔蘚苔原</t>
+          <t>梯田絕景</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>泰國最高處綠色苔蘚森林木棧道、冷溫帶霧林生態解說</t>
+          <t>被譽為泰國最美高山水稻梯田村落、夕陽與稻浪倒影</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>3 小時</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>因他農山頂</t>
+          <t>每年9-11月黃金稻浪</t>
         </is>
       </c>
     </row>
@@ -7233,27 +7233,27 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>卡倫族高山部落 (Karen Hill Tribe Village)</t>
+          <t>Ang Ka 冷溫帶高山步道 (Ang Ka Nature Trail)</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>原住民部落文化</t>
+          <t>高山苔蘚苔原</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>因他農山卡倫族傳統咖啡種植園、高山織布手作工藝展示</t>
+          <t>泰國最高處綠色苔蘚森林木棧道、冷溫帶霧林生態解說</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>因他農山半山腰</t>
+          <t>因他農山頂</t>
         </is>
       </c>
     </row>
@@ -7268,62 +7268,62 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>歐鑾峽谷國家公園 (Ob Luang National Park)</t>
+          <t>卡倫族高山部落 (Karen Hill Tribe Village)</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>峽谷自然景觀</t>
+          <t>原住民部落文化</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>天然岩石巨頭峽谷、紅河吊橋與史前岩畫考古遺蹟</t>
+          <t>因他農山卡倫族傳統咖啡種植園、高山織布手作工藝展示</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>因他農山西南側</t>
+          <t>因他農山半山腰</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>10_清邁至清萊景觀公路區</t>
+          <t>9_因他農山國家公園區</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>布通粘粘瀑布 (Bua Tong Sticky Waterfall)</t>
+          <t>歐鑾峽谷國家公園 (Ob Luang National Park)</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>自然地質奇觀</t>
+          <t>峽谷自然景觀</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>泰國獨一無二地質奇觀！白色鈣化石灰岩瀑布、完全不滑、可以赤腳逆流攀爬瀑布</t>
+          <t>天然岩石巨頭峽谷、紅河吊橋與史前岩畫考古遺蹟</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>美登縣熱門奇觀</t>
+          <t>因他農山西南側</t>
         </is>
       </c>
     </row>
@@ -7338,27 +7338,27 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>清邁藍廟 (Wat Ban Den / 瓦邦頓寺)</t>
+          <t>布通粘粘瀑布 (Bua Tong Sticky Waterfall)</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>地標寺廟/藝術</t>
+          <t>自然地質奇觀</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>美登縣絕美蔚藍神廟群！12生肖佛塔、藍色琉璃瓦大殿與巨大神獸雕刻</t>
+          <t>泰國獨一無二地質奇觀！白色鈣化石灰岩瀑布、完全不滑、可以赤腳逆流攀爬瀑布</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>清邁北部美登縣最震撼寺廟</t>
+          <t>美登縣熱門奇觀</t>
         </is>
       </c>
     </row>
@@ -7373,27 +7373,27 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>美納斯水庫水上木屋 (Mountain Float / Mae Ngat Dam)</t>
+          <t>清邁藍廟 (Wat Ban Den / 瓦邦頓寺)</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>水上度假木屋</t>
+          <t>地標寺廟/藝術</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>美登美納斯水庫天然湖泊、獨木舟、水上漂浮木屋與水中樹倒影秘境</t>
+          <t>美登縣絕美蔚藍神廟群！12生肖佛塔、藍色琉璃瓦大殿與巨大神獸雕刻</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>半天 ~ 1 天</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>美登縣水庫秘境</t>
+          <t>清邁北部美登縣最震撼寺廟</t>
         </is>
       </c>
     </row>
@@ -7408,27 +7408,27 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>Khao Soi Prince (王子咖哩麵)</t>
+          <t>美納斯水庫水上木屋 (Mountain Float / Mae Ngat Dam)</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>米其林必比登美食</t>
+          <t>水上度假木屋</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>米其林必比登推薦！清邁北部名店、濃郁香醇牛腱肉咖哩麵</t>
+          <t>美登美納斯水庫天然湖泊、獨木舟、水上漂浮木屋與水中樹倒影秘境</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>半天 ~ 1 天</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>美登公路途經</t>
+          <t>美登縣水庫秘境</t>
         </is>
       </c>
     </row>
@@ -7443,27 +7443,27 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>美登大象營 (Mae Taeng Elephant Park)</t>
+          <t>Khao Soi Prince (王子咖哩麵)</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>大象體驗</t>
+          <t>米其林必比登美食</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>傳統大象表演、大象繪畫展示與美登河竹筏漂流</t>
+          <t>米其林必比登推薦！清邁北部名店、濃郁香醇牛腱肉咖哩麵</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>3 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>美登縣公路旁</t>
+          <t>美登公路途經</t>
         </is>
       </c>
     </row>
@@ -7478,17 +7478,17 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>美登河急流漂流 (Mae Taeng River Rafting)</t>
+          <t>美登大象營 (Mae Taeng Elephant Park)</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>戶外極限體驗</t>
+          <t>大象體驗</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>泰北最刺激三級至四級白水急流橡皮艇漂流</t>
+          <t>傳統大象表演、大象繪畫展示與美登河竹筏漂流</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>夏季雨季最刺激</t>
+          <t>美登縣公路旁</t>
         </is>
       </c>
     </row>
@@ -7513,27 +7513,27 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>Mae Kachan 天然溫泉中途站</t>
+          <t>美登河急流漂流 (Mae Taeng River Rafting)</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>公路中途站</t>
+          <t>戶外極限體驗</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>118 號公路地熱噴泉、免費露天泡腳池、溫泉蛋體驗</t>
+          <t>泰北最刺激三級至四級白水急流橡皮艇漂流</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>45 分鐘</t>
+          <t>3 小時</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>跨城包車洗手間休息站</t>
+          <t>夏季雨季最刺激</t>
         </is>
       </c>
     </row>
@@ -7548,27 +7548,27 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>孔雀王廟 (Wat Saeng Kaew Phothiyan)</t>
+          <t>Mae Kachan 天然溫泉中途站</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>特色寺廟/地標</t>
+          <t>公路中途站</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>美律縣地標！金光巨型孔雀聖像、巨大象神與夜叉守護神雕像</t>
+          <t>118 號公路地熱噴泉、免費露天泡腳池、溫泉蛋體驗</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>45 分鐘</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>古巴阿里雅查名廟</t>
+          <t>跨城包車洗手間休息站</t>
         </is>
       </c>
     </row>
@@ -7583,27 +7583,27 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>清道溶洞神廟 (Wat Tham Chiang Dao)</t>
+          <t>孔雀王廟 (Wat Saeng Kaew Phothiyan)</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>自然溶洞古寺</t>
+          <t>特色寺廟/地標</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>清道山腳下天然巨大石灰岩溶洞、鐘乳石與洞穴佛像探險</t>
+          <t>美律縣地標！金光巨型孔雀聖像、巨大象神與夜叉守護神雕像</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>清邁北部清道縣</t>
+          <t>古巴阿里雅查名廟</t>
         </is>
       </c>
     </row>
@@ -7618,27 +7618,27 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Chiang Dao Nest</t>
+          <t>清道溶洞神廟 (Wat Tham Chiang Dao)</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>山谷景觀餐廳</t>
+          <t>自然溶洞古寺</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>清道雪山 (Doi Luang Chiang Dao) 腳下高山木屋與精緻泰西料理</t>
+          <t>清道山腳下天然巨大石灰岩溶洞、鐘乳石與洞穴佛像探險</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>雪山絕景</t>
+          <t>清邁北部清道縣</t>
         </is>
       </c>
     </row>
@@ -7653,17 +7653,17 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Baan Na Kang Tong</t>
+          <t>Chiang Dao Nest</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>稻田木屋咖啡</t>
+          <t>山谷景觀餐廳</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>清道高山稻田梯田、高腳木棧道與高山咖啡下午茶</t>
+          <t>清道雪山 (Doi Luang Chiang Dao) 腳下高山木屋與精緻泰西料理</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>清道熱門網美店</t>
+          <t>雪山絕景</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>Villa De Hun</t>
+          <t>Baan Na Kang Tong</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>雪山景觀飯店餐廳</t>
+          <t>稻田木屋咖啡</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>清道大雪山正面全景視角、露天高山咖啡與下午茶</t>
+          <t>清道高山稻田梯田、高腳木棧道與高山咖啡下午茶</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>清道大雪山無遮蔽</t>
+          <t>清道熱門網美店</t>
         </is>
       </c>
     </row>
@@ -7723,27 +7723,27 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>芳縣天然地熱溫泉 (Fang Hot Springs)</t>
+          <t>Villa De Hun</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>天然溫泉國家公園</t>
+          <t>雪山景觀飯店餐廳</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>蒸氣地熱噴泉水柱、露天木桶泡湯與天然溫泉水水療</t>
+          <t>清道大雪山正面全景視角、露天高山咖啡與下午茶</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>清邁最北端芳縣</t>
+          <t>清道大雪山無遮蔽</t>
         </is>
       </c>
     </row>
@@ -7758,17 +7758,17 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>清邁日本城 (Hinoki Land)</t>
+          <t>芳縣天然地熱溫泉 (Fang Hot Springs)</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>日式主題園區</t>
+          <t>天然溫泉國家公園</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>耗資巨額打造日式千本鳥居、檜木城堡與日式和服體驗</t>
+          <t>蒸氣地熱噴泉水柱、露天木桶泡湯與天然溫泉水水療</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>芳縣日式景觀</t>
+          <t>清邁最北端芳縣</t>
         </is>
       </c>
     </row>
@@ -7793,27 +7793,27 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>安康山皇家農業場 (Doi Ang Khang)</t>
+          <t>清邁日本城 (Hinoki Land)</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>高山櫻花谷</t>
+          <t>日式主題園區</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>清邁最美高山櫻花谷、寒帶高山水果蔬菜與高山茶園</t>
+          <t>耗資巨額打造日式千本鳥居、檜木城堡與日式和服體驗</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>3 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>每年1月賞櫻名所</t>
+          <t>芳縣日式景觀</t>
         </is>
       </c>
     </row>
@@ -7828,27 +7828,27 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>蒙恩山雲海茶園 (Mon Ngo Viewpoint)</t>
+          <t>安康山皇家農業場 (Doi Ang Khang)</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>高山日出雲海</t>
+          <t>高山櫻花谷</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>清道山脈絕美雲海日出觀景台與高山茶園</t>
+          <t>清邁最美高山櫻花谷、寒帶高山水果蔬菜與高山茶園</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>3 小時</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>露營熱點</t>
+          <t>每年1月賞櫻名所</t>
         </is>
       </c>
     </row>
@@ -7863,17 +7863,17 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>南邦舍利寺 (Wat Phra That Lampang Luang)</t>
+          <t>蒙恩山雲海茶園 (Mon Ngo Viewpoint)</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>古蹟寺廟/地標</t>
+          <t>高山日出雲海</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>泰國最古老全柚木建築寺廟、傳世佛舍利金塔與影倒立奇景</t>
+          <t>清道山脈絕美雲海日出觀景台與高山茶園</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>南邦府古城</t>
+          <t>露營熱點</t>
         </is>
       </c>
     </row>
@@ -7898,27 +7898,27 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>南邦馬車古城體驗 (Lampang Horse Carriage)</t>
+          <t>南邦舍利寺 (Wat Phra That Lampang Luang)</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>文化體驗</t>
+          <t>古蹟寺廟/地標</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>泰國唯一保留歐式復古馬車計程車巡禮、遊覽南邦古街與老宅</t>
+          <t>泰國最古老全柚木建築寺廟、傳世佛舍利金塔與影倒立奇景</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>南邦市區</t>
+          <t>南邦府古城</t>
         </is>
       </c>
     </row>
@@ -7933,17 +7933,17 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>長頸族文化村 (Long Neck Karen Village)</t>
+          <t>南邦馬車古城體驗 (Lampang Horse Carriage)</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>原住民文化體驗</t>
+          <t>文化體驗</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>阿勛經典必訪！了解泰北長頸族傳統銅環與傳統織布</t>
+          <t>泰國唯一保留歐式復古馬車計程車巡禮、遊覽南邦古街與老宅</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -7953,42 +7953,42 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>美登/清萊途中</t>
+          <t>南邦市區</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>11_清萊市區藝術區</t>
+          <t>10_清邁至清萊景觀公路區</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>LuLum Chiang Rai (柯克河畔泰北菜)</t>
+          <t>長頸族文化村 (Long Neck Karen Village)</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>米其林必比登餐廳</t>
+          <t>原住民文化體驗</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>米其林必比登推薦！清萊最著名柯克河畔景觀餐廳、泰北辣醬與烤豬肋排</t>
+          <t>阿勛經典必訪！了解泰北長頸族傳統銅環與傳統織布</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>清萊第一美饌</t>
+          <t>美登/清萊途中</t>
         </is>
       </c>
     </row>
@@ -8003,27 +8003,27 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Khao Soi San Sai (清萊咖哩麵)</t>
+          <t>LuLum Chiang Rai (柯克河畔泰北菜)</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>米其林必比登小吃</t>
+          <t>米其林必比登餐廳</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>米其林必比登推薦！清萊數十年老字號濃郁泰北雞腿咖哩麵</t>
+          <t>米其林必比登推薦！清萊最著名柯克河畔景觀餐廳、泰北辣醬與烤豬肋排</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>清萊市區</t>
+          <t>清萊第一美饌</t>
         </is>
       </c>
     </row>
@@ -8038,17 +8038,17 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Lab San Pa Koi (泰北辣醬烤肉)</t>
+          <t>Khao Soi San Sai (清萊咖哩麵)</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>米其林必比登美食</t>
+          <t>米其林必比登小吃</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>米其林必比登推薦！泰北道地碎肉辣醬 Lab 與香辣烤豬肉</t>
+          <t>米其林必比登推薦！清萊數十年老字號濃郁泰北雞腿咖哩麵</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>在地老字號</t>
+          <t>清萊市區</t>
         </is>
       </c>
     </row>
@@ -8073,27 +8073,27 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Phu Lae (鳳梨炒飯與泰北菜)</t>
+          <t>Lab San Pa Koi (泰北辣醬烤肉)</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>米其林推薦美饌</t>
+          <t>米其林必比登美食</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>米其林推薦！選用清萊特產小鳳梨做盛器的小鳳梨炒飯與泰北菜</t>
+          <t>米其林必比登推薦！泰北道地碎肉辣醬 Lab 與香辣烤豬肉</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>清萊鐘樓旁</t>
+          <t>在地老字號</t>
         </is>
       </c>
     </row>
@@ -8108,27 +8108,27 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>清萊白廟 (Wat Rong Khun)</t>
+          <t>Phu Lae (鳳梨炒飯與泰北菜)</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>當代藝術寺廟</t>
+          <t>米其林推薦美饌</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>泰國國寶大師傑作！純白雕琢與銀色鏡面、奈何橋與地獄輪迴手</t>
+          <t>米其林推薦！選用清萊特產小鳳梨做盛器的小鳳梨炒飯與泰北菜</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>門票 100 泰銖</t>
+          <t>清萊鐘樓旁</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>清萊藍廟 (Wat Rong Suea Ten)</t>
+          <t>清萊白廟 (Wat Rong Khun)</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -8153,17 +8153,17 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>絢麗寶藍與金黃雕飾大殿、殿內純白巨佛、蝶豆花椰子冰淇淋</t>
+          <t>泰國國寶大師傑作！純白雕琢與銀色鏡面、奈何橋與地獄輪迴手</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>免費參觀</t>
+          <t>門票 100 泰銖</t>
         </is>
       </c>
     </row>
@@ -8178,17 +8178,17 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>清萊黑屋博物館 (Baandam Museum)</t>
+          <t>清萊藍廟 (Wat Rong Suea Ten)</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>藝術博物館</t>
+          <t>當代藝術寺廟</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>鬼才藝術家 Thawan 打造、40多座黑木蘭納建築與動物骨骼標本</t>
+          <t>絢麗寶藍與金黃雕飾大殿、殿內純白巨佛、蝶豆花椰子冰淇淋</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>門票 80 泰銖</t>
+          <t>免費參觀</t>
         </is>
       </c>
     </row>
@@ -8213,17 +8213,17 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>清萊觀音寺 (Wat Huay Pla Kang)</t>
+          <t>清萊黑屋博物館 (Baandam Museum)</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>地標寺廟</t>
+          <t>藝術博物館</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>九層玉塔與90公尺巨型雪白觀音聖像、電梯直達觀音頭部觀景</t>
+          <t>鬼才藝術家 Thawan 打造、40多座黑木蘭納建築與動物骨骼標本</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>清萊市郊地標</t>
+          <t>門票 80 泰銖</t>
         </is>
       </c>
     </row>
@@ -8248,27 +8248,27 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>清萊金黃鐘樓 (Chiang Rai Clock Tower)</t>
+          <t>清萊觀音寺 (Wat Huay Pla Kang)</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>城市地標</t>
+          <t>地標寺廟</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>白廟大師親自設計的金黃璀璨鐘樓、每晚整點燈光音樂秀</t>
+          <t>九層玉塔與90公尺巨型雪白觀音聖像、電梯直達觀音頭部觀景</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>0.5 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>每晚 19:00/20:00/21:00</t>
+          <t>清萊市郊地標</t>
         </is>
       </c>
     </row>
@@ -8283,27 +8283,27 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>聖獅公園 (Singha Park)</t>
+          <t>清萊金黃鐘樓 (Chiang Rai Clock Tower)</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>主題園區</t>
+          <t>城市地標</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>巨型金獅地標、茶園熱氣球體驗、天鵝湖與花海溜索</t>
+          <t>白廟大師親自設計的金黃璀璨鐘樓、每晚整點燈光音樂秀</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>0.5 小時</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>園區遊園車極方便</t>
+          <t>每晚 19:00/20:00/21:00</t>
         </is>
       </c>
     </row>
@@ -8318,27 +8318,27 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Melt in Your Mouth</t>
+          <t>聖獅公園 (Singha Park)</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>柯克河畔餐廳</t>
+          <t>主題園區</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>柯克河畔英式白色歐風莊園餐廳、甜點與泰西融合料理</t>
+          <t>巨型金獅地標、茶園熱氣球體驗、天鵝湖與花海溜索</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>清萊水岸名店</t>
+          <t>園區遊園車極方便</t>
         </is>
       </c>
     </row>
@@ -8353,17 +8353,17 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>清萊夜市 (Chiang Rai Night Bazaar)</t>
+          <t>Melt in Your Mouth</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>傳統夜市</t>
+          <t>柯克河畔餐廳</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>市中心夜市、露天舞台傳統舞蹈表演與陶鍋小火鍋</t>
+          <t>柯克河畔英式白色歐風莊園餐廳、甜點與泰西融合料理</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>晚上熱門</t>
+          <t>清萊水岸名店</t>
         </is>
       </c>
     </row>
@@ -8388,27 +8388,27 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>清萊玉佛寺 (Wat Phra Kaew Chiang Rai)</t>
+          <t>清萊夜市 (Chiang Rai Night Bazaar)</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>古蹟寺廟</t>
+          <t>傳統夜市</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>泰國玉佛發源地歷史名寺、綠玉佛複製像與博物館</t>
+          <t>市中心夜市、露天舞台傳統舞蹈表演與陶鍋小火鍋</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>清萊市區</t>
+          <t>晚上熱門</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>城柱山頂古寺 (Wat Phra That Doi Chom Thong)</t>
+          <t>清萊玉佛寺 (Wat Phra Kaew Chiang Rai)</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>清萊建城古寺、俯瞰清萊市區全景與柯克河</t>
+          <t>泰國玉佛發源地歷史名寺、綠玉佛複製像與博物館</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>清萊地標</t>
+          <t>清萊市區</t>
         </is>
       </c>
     </row>
@@ -8458,27 +8458,27 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>南奔哈利奔猜大金塔寺 (Wat Phra That Hariphunchai)</t>
+          <t>城柱山頂古寺 (Wat Phra That Doi Chom Thong)</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>古蹟寺廟/地標</t>
+          <t>古蹟寺廟</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>南奔府千年皇家大金塔寺、泰國雞年本命年祈福聖地</t>
+          <t>清萊建城古寺、俯瞰清萊市區全景與柯克河</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>清邁南郊南奔府</t>
+          <t>清萊地標</t>
         </is>
       </c>
     </row>
@@ -8493,27 +8493,27 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>南奔 Chamadevi 方塔寺 (Wat Chama Devi)</t>
+          <t>南奔哈利奔猜大金塔寺 (Wat Phra That Hariphunchai)</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>古蹟寺廟</t>
+          <t>古蹟寺廟/地標</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>陀羅缽地王朝金剛寶座風格方形佛塔遺蹟</t>
+          <t>南奔府千年皇家大金塔寺、泰國雞年本命年祈福聖地</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>南奔府古寺</t>
+          <t>清邁南郊南奔府</t>
         </is>
       </c>
     </row>
@@ -8528,62 +8528,62 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>象神博物館 (Ganesh Museum Chiang Mai)</t>
+          <t>南奔 Chamadevi 方塔寺 (Wat Chama Devi)</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>主題博物館</t>
+          <t>古蹟寺廟</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>泰國最大象神雕像博物館、收集世界各地數千尊象神藝術品</t>
+          <t>陀羅缽地王朝金剛寶座風格方形佛塔遺蹟</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>泰國祈福名所</t>
+          <t>南奔府古寺</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>12_茶園與金三角</t>
+          <t>11_清萊市區藝術區</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>Lalitta Café (清萊仙境瀑布咖啡)</t>
+          <t>象神博物館 (Ganesh Museum Chiang Mai)</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>網美瀑布咖啡</t>
+          <t>主題博物館</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>柯克河畔夢幻水霧瀑布、仙女雕像與雨林花園秘境</t>
+          <t>泰國最大象神雕像博物館、收集世界各地數千尊象神藝術品</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>入場費可全額折抵餐飲</t>
+          <t>泰國祈福名所</t>
         </is>
       </c>
     </row>
@@ -8598,17 +8598,17 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>翠峰茶園 (Choui Fong Tea Plantation)</t>
+          <t>Lalitta Café (清萊仙境瀑布咖啡)</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>高山茶園觀景</t>
+          <t>網美瀑布咖啡</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>綿延綠色梯田茶山、360度極簡觀景台、招牌抹茶蛋糕與冷泡烏龍</t>
+          <t>柯克河畔夢幻水霧瀑布、仙女雕像與雨林花園秘境</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>清萊最美茶園</t>
+          <t>入場費可全額折抵餐飲</t>
         </is>
       </c>
     </row>
@@ -8633,27 +8633,27 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>美斯樂高山村 (Doi Mae Salong)</t>
+          <t>翠峰茶園 (Choui Fong Tea Plantation)</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>高山歷史名村</t>
+          <t>高山茶園觀景</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>泰北孤軍歷史故事村、高山烏龍茶園與櫻花步道景觀</t>
+          <t>綿延綠色梯田茶山、360度極簡觀景台、招牌抹茶蛋糕與冷泡烏龍</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>3 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>高山雲霧村落</t>
+          <t>清萊最美茶園</t>
         </is>
       </c>
     </row>
@@ -8668,27 +8668,27 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>金三角 (Golden Triangle / Chiang Saen)</t>
+          <t>美斯樂高山村 (Doi Mae Salong)</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>歷史邊境地標</t>
+          <t>高山歷史名村</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>泰、寮、緬三國交界湄公河畔、大佛巨船與鴉片博物館</t>
+          <t>泰北孤軍歷史故事村、高山烏龍茶園與櫻花步道景觀</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>3 小時</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>可乘坐長尾船遊湄公河</t>
+          <t>高山雲霧村落</t>
         </is>
       </c>
     </row>
@@ -8703,17 +8703,17 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>鴉片博物館 (Hall of Opium)</t>
+          <t>金三角 (Golden Triangle / Chiang Saen)</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>歷史博物館</t>
+          <t>歷史邊境地標</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>展示金三角鴉片貿易歷史、禁毒教育與沈浸式多媒體展覽</t>
+          <t>泰、寮、緬三國交界湄公河畔、大佛巨船與鴉片博物館</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>金三角旁</t>
+          <t>可乘坐長尾船遊湄公河</t>
         </is>
       </c>
     </row>
@@ -8738,27 +8738,27 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>皇太后行宮與花園 (Doi Tung Royal Villa)</t>
+          <t>鴉片博物館 (Hall of Opium)</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>皇室高山花園</t>
+          <t>歷史博物館</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>瑞士木屋風皇太后行宮、四季高山花卉花海公園</t>
+          <t>展示金三角鴉片貿易歷史、禁毒教育與沈浸式多媒體展覽</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>清萊北部最高峰</t>
+          <t>金三角旁</t>
         </is>
       </c>
     </row>
@@ -8773,27 +8773,27 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>指天山觀景台 (Phu Chi Fah)</t>
+          <t>皇太后行宮與花園 (Doi Tung Royal Villa)</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>邊境高山雲海</t>
+          <t>皇室高山花園</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>泰寮邊境絕美懸崖日出與壯觀雲海景觀平台</t>
+          <t>瑞士木屋風皇太后行宮、四季高山花卉花海公園</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>3 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>清萊東部高山</t>
+          <t>清萊北部最高峰</t>
         </is>
       </c>
     </row>
@@ -8808,27 +8808,27 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>美塞泰緬邊境大門 (Mae Sai Border Market)</t>
+          <t>指天山觀景台 (Phu Chi Fah)</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>邊境市場</t>
+          <t>邊境高山雲海</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>泰國最北端邊境關卡、泰緬跨國橋樑與邊境採買市場</t>
+          <t>泰寮邊境絕美懸崖日出與壯觀雲海景觀平台</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>3 小時</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>泰國最北點標誌</t>
+          <t>清萊東部高山</t>
         </is>
       </c>
     </row>
@@ -8843,27 +8843,27 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>象山高山咖啡莊園 (Doi Chang Coffee Farm)</t>
+          <t>美塞泰緬邊境大門 (Mae Sai Border Market)</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>精品咖啡源頭</t>
+          <t>邊境市場</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>泰國最著名 Doi Chaang 象山咖啡原產地、高山採豆與烘豆體驗</t>
+          <t>泰國最北端邊境關卡、泰緬跨國橋樑與邊境採買市場</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>2.5 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>象山高山</t>
+          <t>泰國最北點標誌</t>
         </is>
       </c>
     </row>
@@ -8878,27 +8878,27 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Chouat Cafe &amp; Waterfall</t>
+          <t>象山高山咖啡莊園 (Doi Chang Coffee Farm)</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>水岸瀑布咖啡</t>
+          <t>精品咖啡源頭</t>
         </is>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>清萊水岸高山瀑布觀景台、自然芬多精與特調冷飲</t>
+          <t>泰國最著名 Doi Chaang 象山咖啡原產地、高山採豆與烘豆體驗</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>2.5 小時</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>清萊山區</t>
+          <t>象山高山</t>
         </is>
       </c>
     </row>
@@ -8913,17 +8913,17 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>百萬啤酒瓶寺 (Wat Pa Maha Chedi Kaew)</t>
+          <t>Chouat Cafe &amp; Waterfall</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>奇趣寺廟</t>
+          <t>水岸瀑布咖啡</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>由超過 150 萬個海尼根與泰國啤酒綠色玻璃瓶建造的綠光寺廟</t>
+          <t>清萊水岸高山瀑布觀景台、自然芬多精與特調冷飲</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>泰北奇觀</t>
+          <t>清萊山區</t>
         </is>
       </c>
     </row>
@@ -8948,27 +8948,27 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>拜縣樹屋度假村咖啡 (Pai Treehouse Resort)</t>
+          <t>百萬啤酒瓶寺 (Wat Pa Maha Chedi Kaew)</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>高山樹屋咖啡</t>
+          <t>奇趣寺廟</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>拜縣經典地標！巨大樹木與木造高空樹屋咖啡、俯瞰拜河景致</t>
+          <t>由超過 150 萬個海尼根與泰國啤酒綠色玻璃瓶建造的綠光寺廟</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>2 小時</t>
+          <t>1.5 小時</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>拜縣熱門打卡</t>
+          <t>泰北奇觀</t>
         </is>
       </c>
     </row>
@@ -8983,17 +8983,17 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>拜縣雲來觀景台 (Yun Lai Viewpoint Pai)</t>
+          <t>拜縣樹屋度假村咖啡 (Pai Treehouse Resort)</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>高山日出雲海</t>
+          <t>高山樹屋咖啡</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>拜縣雲頂中華村觀景平台、俯瞰高山雲霧與品嚐熱烏龍茶</t>
+          <t>拜縣經典地標！巨大樹木與木造高空樹屋咖啡、俯瞰拜河景致</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>拜縣高山</t>
+          <t>拜縣熱門打卡</t>
         </is>
       </c>
     </row>
@@ -9018,17 +9018,17 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>拜縣大峽谷 (Pai Canyon / 孔敬峽谷)</t>
+          <t>拜縣雲來觀景台 (Yun Lai Viewpoint Pai)</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>自然地質奇景</t>
+          <t>高山日出雲海</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>阿勛經典必訪！極窄紅土崖壁走廊、觀賞夕陽餘暉名所</t>
+          <t>拜縣雲頂中華村觀景平台、俯瞰高山雲霧與品嚐熱烏龍茶</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>拜縣經典</t>
+          <t>拜縣高山</t>
         </is>
       </c>
     </row>
@@ -9053,27 +9053,27 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>拜縣二戰紀念大橋 (Memorial Bridge Pai)</t>
+          <t>拜縣大峽谷 (Pai Canyon / 孔敬峽谷)</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>歷史地標</t>
+          <t>自然地質奇景</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>二戰時期鋼架古橋、拜河河畔打卡地標</t>
+          <t>阿勛經典必訪！極窄紅土崖壁走廊、觀賞夕陽餘暉名所</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>1 小時</t>
+          <t>2 小時</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>拜縣公路旁</t>
+          <t>拜縣經典</t>
         </is>
       </c>
     </row>
@@ -9088,27 +9088,27 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>拜縣山地村 (Santichon Village)</t>
+          <t>拜縣二戰紀念大橋 (Memorial Bridge Pai)</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>雲南民俗村</t>
+          <t>歷史地標</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>泰北雲南村落、傳統土生住宅、品嚐雲南大頭菜與高山茶</t>
+          <t>二戰時期鋼架古橋、拜河河畔打卡地標</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>1.5 小時</t>
+          <t>1 小時</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>雲來觀景台山腳</t>
+          <t>拜縣公路旁</t>
         </is>
       </c>
     </row>
@@ -9123,25 +9123,60 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
+          <t>拜縣山地村 (Santichon Village)</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>雲南民俗村</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>泰北雲南村落、傳統土生住宅、品嚐雲南大頭菜與高山茶</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>1.5 小時</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>雲來觀景台山腳</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>12_茶園與金三角</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
           <t>拜縣美音寺大佛 (Wat Phra That Mae Yen)</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>地標寺廟/觀景</t>
         </is>
       </c>
-      <c r="E248" s="3" t="inlineStr">
+      <c r="E249" s="3" t="inlineStr">
         <is>
           <t>山頂純白巨型坐佛、353階梯登頂俯瞰整座拜縣山谷夕陽</t>
         </is>
       </c>
-      <c r="F248" s="3" t="inlineStr">
+      <c r="F249" s="3" t="inlineStr">
         <is>
           <t>1.5 小時</t>
         </is>
       </c>
-      <c r="G248" s="3" t="inlineStr">
+      <c r="G249" s="3" t="inlineStr">
         <is>
           <t>拜縣夕陽勝地</t>
         </is>
